--- a/daily/2026-03-29.xlsx
+++ b/daily/2026-03-29.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E3" t="n">
         <v>11.7</v>
@@ -684,13 +684,13 @@
         <v>5.9</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="R3" t="n">
         <v>4.3</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="E6" t="n">
         <v>27.7</v>
@@ -930,13 +930,13 @@
         <v>5.7</v>
       </c>
       <c r="O6" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
         <v>-0.4</v>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="E8" t="n">
         <v>4.3</v>
@@ -1090,13 +1090,13 @@
         <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
         <v>-4.5</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="E9" t="n">
         <v>16.3</v>
@@ -1168,13 +1168,13 @@
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="R9" t="n">
         <v>2.8</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E13" t="n">
         <v>11.3</v>
@@ -1498,7 +1498,7 @@
         <v>70</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="R13" t="n">
         <v>-0.5</v>
@@ -1527,7 +1527,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1541,55 +1541,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E14" t="n">
-        <v>18.3</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>18.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>18.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>18.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>20.7</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="K14" t="n">
-        <v>29</v>
+        <v>26.2</v>
       </c>
       <c r="L14" t="n">
-        <v>45.3</v>
+        <v>50.1</v>
       </c>
       <c r="M14" t="n">
-        <v>46.1</v>
+        <v>46.7</v>
       </c>
       <c r="N14" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1.3</v>
       </c>
       <c r="U14" t="n">
         <v>22</v>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>17.0 (3g)</t>
+          <t>6.0 (5g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>-16.7</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1619,79 +1619,79 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="F15" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="G15" t="n">
-        <v>9.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>15.1</v>
       </c>
       <c r="J15" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>26.2</v>
+        <v>29.2</v>
       </c>
       <c r="L15" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="M15" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>60</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6.0 (5g)</t>
+          <t>7.5 (6g)</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-11.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1701,73 +1701,73 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>12.5</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="F16" t="n">
-        <v>14.2</v>
+        <v>12.2</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="H16" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="I16" t="n">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="K16" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="L16" t="n">
-        <v>50.8</v>
+        <v>47.6</v>
       </c>
       <c r="M16" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
         <v>50</v>
       </c>
-      <c r="N16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>60</v>
-      </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>7.5 (6g)</t>
+          <t>6.7 (3g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>9.6</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="17">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E20" t="n">
         <v>16.3</v>
@@ -2065,10 +2065,10 @@
         <v>50</v>
       </c>
       <c r="P20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
         <v>-2.1</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="E21" t="n">
         <v>15.7</v>
@@ -2144,13 +2144,13 @@
         <v>6.9</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P21" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7</v>
+        <v>-1.3</v>
       </c>
       <c r="R21" t="n">
         <v>-2.6</v>
@@ -2261,7 +2261,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2275,80 +2275,80 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H23" t="n">
         <v>13.5</v>
       </c>
-      <c r="E23" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>14.4</v>
-      </c>
       <c r="I23" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="J23" t="n">
-        <v>30.1</v>
+        <v>26.3</v>
       </c>
       <c r="K23" t="n">
-        <v>29.9</v>
+        <v>27.5</v>
       </c>
       <c r="L23" t="n">
-        <v>53.1</v>
+        <v>49.9</v>
       </c>
       <c r="M23" t="n">
-        <v>42.1</v>
+        <v>46.1</v>
       </c>
       <c r="N23" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P23" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.2</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S23" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="U23" t="n">
         <v>22</v>
       </c>
       <c r="V23" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.3 (3g)</t>
+          <t>11.2 (6g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-13.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOS @ CHA</t>
+          <t>MIA @ IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2357,75 +2357,75 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
       <c r="E24" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="F24" t="n">
-        <v>22.2</v>
+        <v>15.8</v>
       </c>
       <c r="G24" t="n">
-        <v>22.4</v>
+        <v>17.5</v>
       </c>
       <c r="H24" t="n">
-        <v>20.9</v>
+        <v>14.4</v>
       </c>
       <c r="I24" t="n">
-        <v>20.1</v>
+        <v>13.7</v>
       </c>
       <c r="J24" t="n">
-        <v>28.6</v>
+        <v>30.1</v>
       </c>
       <c r="K24" t="n">
-        <v>28.3</v>
+        <v>29.9</v>
       </c>
       <c r="L24" t="n">
-        <v>44.9</v>
+        <v>53.1</v>
       </c>
       <c r="M24" t="n">
-        <v>40.9</v>
+        <v>42.1</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
         <v>2.1</v>
       </c>
       <c r="S24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>22</v>
+      </c>
+      <c r="V24" t="n">
         <v>4</v>
       </c>
-      <c r="T24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>24</v>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>28.3 (3g)</t>
+          <t>9.3 (3g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>7.3</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,75 +2439,75 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="F25" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="G25" t="n">
-        <v>17.1</v>
+        <v>22.4</v>
       </c>
       <c r="H25" t="n">
-        <v>15.8</v>
+        <v>20.9</v>
       </c>
       <c r="I25" t="n">
-        <v>17.2</v>
+        <v>20.1</v>
       </c>
       <c r="J25" t="n">
-        <v>33.2</v>
+        <v>28.6</v>
       </c>
       <c r="K25" t="n">
-        <v>32.4</v>
+        <v>28.3</v>
       </c>
       <c r="L25" t="n">
-        <v>43.2</v>
+        <v>44.9</v>
       </c>
       <c r="M25" t="n">
-        <v>42.5</v>
+        <v>40.9</v>
       </c>
       <c r="N25" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
+        <v>80</v>
+      </c>
+      <c r="P25" t="n">
         <v>60</v>
       </c>
-      <c r="P25" t="n">
-        <v>55</v>
-      </c>
       <c r="Q25" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="U25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>17.0 (5g)</t>
+          <t>28.3 (3g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2521,55 +2521,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="E26" t="n">
-        <v>12.3</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>12.4</v>
+        <v>19.6</v>
       </c>
       <c r="G26" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H26" t="n">
         <v>15.8</v>
       </c>
-      <c r="H26" t="n">
-        <v>16.5</v>
-      </c>
       <c r="I26" t="n">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="J26" t="n">
-        <v>34.1</v>
+        <v>33.2</v>
       </c>
       <c r="K26" t="n">
-        <v>34.4</v>
+        <v>32.4</v>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>43.2</v>
       </c>
       <c r="M26" t="n">
-        <v>38</v>
+        <v>42.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P26" t="n">
         <v>45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.4</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>-0</v>
+        <v>0.7</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="U26" t="n">
         <v>9</v>
@@ -2579,17 +2579,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>20.8 (4g)</t>
+          <t>17.0 (5g)</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2599,79 +2599,79 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="E27" t="n">
-        <v>20.3</v>
+        <v>12.3</v>
       </c>
       <c r="F27" t="n">
-        <v>19.6</v>
+        <v>12.4</v>
       </c>
       <c r="G27" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="I27" t="n">
-        <v>24.1</v>
+        <v>15.8</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>34.1</v>
       </c>
       <c r="K27" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="L27" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>41.9</v>
+        <v>38</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="O27" t="n">
         <v>30</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.6</v>
+        <v>-1.7</v>
       </c>
       <c r="R27" t="n">
-        <v>-4.5</v>
+        <v>-3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.6</v>
+        <v>-0</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.7</v>
+        <v>-0.3</v>
       </c>
       <c r="U27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
         <v>17</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>25.7 (3g)</t>
+          <t>20.8 (4g)</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2685,65 +2685,69 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="E28" t="n">
-        <v>4.7</v>
+        <v>20.3</v>
       </c>
       <c r="F28" t="n">
-        <v>3.8</v>
+        <v>19.6</v>
       </c>
       <c r="G28" t="n">
-        <v>5.8</v>
+        <v>19.8</v>
       </c>
       <c r="H28" t="n">
-        <v>7.3</v>
+        <v>22</v>
       </c>
       <c r="I28" t="n">
-        <v>6.8</v>
+        <v>24.1</v>
       </c>
       <c r="J28" t="n">
-        <v>18.6</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>19.5</v>
+        <v>34.7</v>
       </c>
       <c r="L28" t="n">
-        <v>41.4</v>
+        <v>38.2</v>
       </c>
       <c r="M28" t="n">
-        <v>39.8</v>
+        <v>41.9</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="P28" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>-3</v>
+        <v>-4.5</v>
       </c>
       <c r="S28" t="n">
-        <v>1.7</v>
+        <v>-3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.9</v>
+        <v>-3.7</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28" t="n">
-        <v>24</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>25.7 (3g)</t>
+        </is>
+      </c>
       <c r="X28" t="n">
-        <v>-12.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="29">
@@ -3087,7 +3091,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E33" t="n">
         <v>7.3</v>
@@ -3123,10 +3127,10 @@
         <v>30</v>
       </c>
       <c r="P33" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="R33" t="n">
         <v>-0.9</v>
@@ -3251,7 +3255,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="E35" t="n">
         <v>17</v>
@@ -3287,10 +3291,10 @@
         <v>40</v>
       </c>
       <c r="P35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="R35" t="n">
         <v>-3.5</v>
@@ -3315,7 +3319,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3325,69 +3329,73 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>32.6</v>
+        <v>5.4</v>
       </c>
       <c r="G36" t="n">
-        <v>26.8</v>
+        <v>7.5</v>
       </c>
       <c r="H36" t="n">
-        <v>26.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>27.4</v>
+        <v>9.5</v>
       </c>
       <c r="J36" t="n">
-        <v>34.4</v>
+        <v>25.3</v>
       </c>
       <c r="K36" t="n">
-        <v>34.6</v>
+        <v>27</v>
       </c>
       <c r="L36" t="n">
-        <v>46.6</v>
+        <v>33.8</v>
       </c>
       <c r="M36" t="n">
-        <v>46.3</v>
+        <v>39.4</v>
       </c>
       <c r="N36" t="n">
-        <v>9.5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P36" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9</v>
+        <v>-0</v>
       </c>
       <c r="R36" t="n">
-        <v>5.2</v>
+        <v>-4.1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.3</v>
+        <v>-5.6</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.2</v>
+        <v>-1.7</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36" t="n">
         <v>17</v>
       </c>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>10.4 (5g)</t>
+        </is>
+      </c>
       <c r="X36" t="n">
-        <v>-6.7</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="37">
@@ -3571,7 +3579,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E39" t="n">
         <v>14.7</v>
@@ -3604,13 +3612,13 @@
         <v>9.1</v>
       </c>
       <c r="O39" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P39" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="R39" t="n">
         <v>4.8</v>
@@ -4281,7 +4289,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E48" t="n">
         <v>19</v>
@@ -4314,13 +4322,13 @@
         <v>7.1</v>
       </c>
       <c r="O48" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P48" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="R48" t="n">
         <v>4</v>
@@ -4687,7 +4695,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="E53" t="n">
         <v>14.7</v>
@@ -4726,7 +4734,7 @@
         <v>45</v>
       </c>
       <c r="Q53" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R53" t="n">
         <v>5.7</v>
@@ -4851,7 +4859,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E55" t="n">
         <v>9.300000000000001</v>
@@ -4890,7 +4898,7 @@
         <v>35</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R55" t="n">
         <v>2.5</v>
@@ -5001,7 +5009,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5011,75 +5019,75 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="n">
-        <v>17.7</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>15</v>
+        <v>17.4</v>
       </c>
       <c r="G57" t="n">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="H57" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I57" t="n">
         <v>12.4</v>
       </c>
-      <c r="I57" t="n">
-        <v>12.9</v>
-      </c>
       <c r="J57" t="n">
-        <v>30.7</v>
+        <v>28.8</v>
       </c>
       <c r="K57" t="n">
-        <v>32.2</v>
+        <v>26.2</v>
       </c>
       <c r="L57" t="n">
-        <v>47.8</v>
+        <v>44.9</v>
       </c>
       <c r="M57" t="n">
-        <v>43.7</v>
+        <v>45.8</v>
       </c>
       <c r="N57" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="O57" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P57" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1.6</v>
+        <v>-0.1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>-0.9</v>
       </c>
       <c r="T57" t="n">
-        <v>-1.5</v>
+        <v>2.6</v>
       </c>
       <c r="U57" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="V57" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
-        <v>6.1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5089,75 +5097,79 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>16.5</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G58" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="H58" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="I58" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
       <c r="J58" t="n">
-        <v>24.1</v>
+        <v>27.5</v>
       </c>
       <c r="K58" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="L58" t="n">
-        <v>43.9</v>
+        <v>49.2</v>
       </c>
       <c r="M58" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N58" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="O58" t="n">
+        <v>40</v>
+      </c>
+      <c r="P58" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U58" t="n">
         <v>30</v>
-      </c>
-      <c r="P58" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>24</v>
       </c>
       <c r="V58" t="n">
         <v>11</v>
       </c>
-      <c r="W58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>9.7 (3g)</t>
+        </is>
+      </c>
       <c r="X58" t="n">
-        <v>-4</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5167,79 +5179,75 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="E59" t="n">
-        <v>15.7</v>
+        <v>17.7</v>
       </c>
       <c r="F59" t="n">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="G59" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="H59" t="n">
-        <v>17</v>
+        <v>12.4</v>
       </c>
       <c r="I59" t="n">
-        <v>16.4</v>
+        <v>12.9</v>
       </c>
       <c r="J59" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="K59" t="n">
-        <v>28.5</v>
+        <v>32.2</v>
       </c>
       <c r="L59" t="n">
-        <v>39.7</v>
+        <v>47.8</v>
       </c>
       <c r="M59" t="n">
-        <v>46.1</v>
+        <v>43.7</v>
       </c>
       <c r="N59" t="n">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="O59" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P59" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q59" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="R59" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="S59" t="n">
-        <v>-6.4</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
-        <v>1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="U59" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="V59" t="n">
         <v>11</v>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>10.6 (5g)</t>
-        </is>
-      </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
-        <v>-6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sidy Cissoko</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5249,75 +5257,75 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="n">
-        <v>2.3</v>
+        <v>13.3</v>
       </c>
       <c r="F60" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>10.7</v>
       </c>
       <c r="J60" t="n">
-        <v>14</v>
+        <v>17.1</v>
       </c>
       <c r="K60" t="n">
-        <v>19.2</v>
+        <v>15.4</v>
       </c>
       <c r="L60" t="n">
-        <v>32.1</v>
+        <v>49.7</v>
       </c>
       <c r="M60" t="n">
-        <v>36</v>
+        <v>48.4</v>
       </c>
       <c r="N60" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="O60" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="Q60" t="n">
-        <v>-2.9</v>
+        <v>-1.8</v>
       </c>
       <c r="R60" t="n">
-        <v>-1.8</v>
+        <v>1.3</v>
       </c>
       <c r="S60" t="n">
-        <v>-3.9</v>
+        <v>1.3</v>
       </c>
       <c r="T60" t="n">
-        <v>-5.2</v>
+        <v>1.7</v>
       </c>
       <c r="U60" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V60" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
-        <v>-46.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5327,79 +5335,75 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26.5</v>
+        <v>16.5</v>
       </c>
       <c r="E61" t="n">
-        <v>18.7</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>20.8</v>
+        <v>13.8</v>
       </c>
       <c r="G61" t="n">
-        <v>21.8</v>
+        <v>14.7</v>
       </c>
       <c r="H61" t="n">
-        <v>19.6</v>
+        <v>13.7</v>
       </c>
       <c r="I61" t="n">
-        <v>22.3</v>
+        <v>12.8</v>
       </c>
       <c r="J61" t="n">
-        <v>32.3</v>
+        <v>24.1</v>
       </c>
       <c r="K61" t="n">
-        <v>31.6</v>
+        <v>24</v>
       </c>
       <c r="L61" t="n">
-        <v>45.6</v>
+        <v>43.9</v>
       </c>
       <c r="M61" t="n">
-        <v>43.6</v>
+        <v>39</v>
       </c>
       <c r="N61" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="O61" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Q61" t="n">
-        <v>-4.2</v>
+        <v>-3.7</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="T61" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="U61" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="V61" t="n">
         <v>11</v>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>12.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5409,59 +5413,59 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="E62" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="F62" t="n">
-        <v>17.4</v>
+        <v>15.2</v>
       </c>
       <c r="G62" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="H62" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="I62" t="n">
-        <v>12.4</v>
+        <v>13.9</v>
       </c>
       <c r="J62" t="n">
-        <v>28.8</v>
+        <v>32.6</v>
       </c>
       <c r="K62" t="n">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
       <c r="L62" t="n">
-        <v>44.9</v>
+        <v>43.9</v>
       </c>
       <c r="M62" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
       <c r="N62" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="O62" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.1</v>
+        <v>-2.6</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.9</v>
+        <v>-3.3</v>
       </c>
       <c r="T62" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="U62" t="n">
         <v>20</v>
@@ -5471,13 +5475,13 @@
       </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
-        <v>21</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5491,55 +5495,55 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>13.2</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>14.3</v>
+        <v>8.1</v>
       </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>7.2</v>
       </c>
       <c r="J63" t="n">
-        <v>27.5</v>
+        <v>18.8</v>
       </c>
       <c r="K63" t="n">
-        <v>27.2</v>
+        <v>17.3</v>
       </c>
       <c r="L63" t="n">
-        <v>49.2</v>
+        <v>60.5</v>
       </c>
       <c r="M63" t="n">
-        <v>51</v>
+        <v>69.7</v>
       </c>
       <c r="N63" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O63" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P63" t="n">
         <v>35</v>
       </c>
       <c r="Q63" t="n">
-        <v>-3.9</v>
+        <v>-1.3</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="S63" t="n">
-        <v>-1.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T63" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="U63" t="n">
         <v>30</v>
@@ -5547,19 +5551,15 @@
       <c r="V63" t="n">
         <v>11</v>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>9.7 (3g)</t>
-        </is>
-      </c>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
-        <v>-13.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5569,75 +5569,79 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="E64" t="n">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="G64" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="H64" t="n">
-        <v>11.2</v>
+        <v>17</v>
       </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>16.4</v>
       </c>
       <c r="J64" t="n">
-        <v>17.1</v>
+        <v>29.6</v>
       </c>
       <c r="K64" t="n">
-        <v>15.4</v>
+        <v>28.5</v>
       </c>
       <c r="L64" t="n">
-        <v>49.7</v>
+        <v>39.7</v>
       </c>
       <c r="M64" t="n">
-        <v>48.4</v>
+        <v>46.1</v>
       </c>
       <c r="N64" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="O64" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q64" t="n">
-        <v>-1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="R64" t="n">
-        <v>1.3</v>
+        <v>-2.8</v>
       </c>
       <c r="S64" t="n">
-        <v>1.3</v>
+        <v>-6.4</v>
       </c>
       <c r="T64" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="U64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V64" t="n">
-        <v>19</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>10.6 (5g)</t>
+        </is>
+      </c>
       <c r="X64" t="n">
-        <v>-5</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Sidy Cissoko</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5647,75 +5651,75 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E65" t="n">
-        <v>17.3</v>
+        <v>2.3</v>
       </c>
       <c r="F65" t="n">
-        <v>15.2</v>
+        <v>2.8</v>
       </c>
       <c r="G65" t="n">
-        <v>15.3</v>
+        <v>3.4</v>
       </c>
       <c r="H65" t="n">
-        <v>14.6</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>13.9</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
-        <v>32.6</v>
+        <v>14</v>
       </c>
       <c r="K65" t="n">
-        <v>28.2</v>
+        <v>19.2</v>
       </c>
       <c r="L65" t="n">
-        <v>43.9</v>
+        <v>32.1</v>
       </c>
       <c r="M65" t="n">
-        <v>47.3</v>
+        <v>36</v>
       </c>
       <c r="N65" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
-        <v>-2.6</v>
+        <v>-2.9</v>
       </c>
       <c r="R65" t="n">
-        <v>1.3</v>
+        <v>-1.8</v>
       </c>
       <c r="S65" t="n">
-        <v>-3.3</v>
+        <v>-3.9</v>
       </c>
       <c r="T65" t="n">
-        <v>4.5</v>
+        <v>-5.2</v>
       </c>
       <c r="U65" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V65" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
-        <v>45.8</v>
+        <v>-46.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5725,59 +5729,59 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
       <c r="E66" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>20.8</v>
       </c>
       <c r="G66" t="n">
-        <v>8.199999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="H66" t="n">
-        <v>8.1</v>
+        <v>19.6</v>
       </c>
       <c r="I66" t="n">
-        <v>7.2</v>
+        <v>22.3</v>
       </c>
       <c r="J66" t="n">
-        <v>18.8</v>
+        <v>32.3</v>
       </c>
       <c r="K66" t="n">
-        <v>17.3</v>
+        <v>31.6</v>
       </c>
       <c r="L66" t="n">
-        <v>60.5</v>
+        <v>45.6</v>
       </c>
       <c r="M66" t="n">
-        <v>69.7</v>
+        <v>43.6</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="O66" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1.3</v>
+        <v>-4.2</v>
       </c>
       <c r="R66" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="S66" t="n">
-        <v>-9.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
@@ -5785,9 +5789,13 @@
       <c r="V66" t="n">
         <v>11</v>
       </c>
-      <c r="W66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>12.3 (3g)</t>
+        </is>
+      </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="67">
@@ -5889,7 +5897,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E68" t="n">
         <v>12.7</v>
@@ -5922,13 +5930,13 @@
         <v>4.7</v>
       </c>
       <c r="O68" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P68" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q68" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="R68" t="n">
         <v>0.9</v>
@@ -6463,7 +6471,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="E75" t="n">
         <v>21.7</v>
@@ -6496,13 +6504,13 @@
         <v>4</v>
       </c>
       <c r="O75" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P75" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="R75" t="n">
         <v>0.8</v>
@@ -6955,7 +6963,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E81" t="n">
         <v>11</v>
@@ -6988,13 +6996,13 @@
         <v>5.2</v>
       </c>
       <c r="O81" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P81" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="R81" t="n">
         <v>-1.8</v>
@@ -7279,7 +7287,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="n">
         <v>14</v>
@@ -7312,13 +7320,13 @@
         <v>7.5</v>
       </c>
       <c r="O85" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P85" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R85" t="n">
         <v>4.4</v>
@@ -7841,7 +7849,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E92" t="n">
         <v>14.3</v>
@@ -7877,10 +7885,10 @@
         <v>70</v>
       </c>
       <c r="P92" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="R92" t="n">
         <v>1.1</v>
@@ -7987,7 +7995,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7997,79 +8005,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8.5</v>
+        <v>15.5</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>21.3</v>
       </c>
       <c r="F94" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H94" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I94" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K94" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L94" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="M94" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="N94" t="n">
         <v>7.4</v>
-      </c>
-      <c r="G94" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H94" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I94" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J94" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="K94" t="n">
-        <v>28</v>
-      </c>
-      <c r="L94" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="M94" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="N94" t="n">
-        <v>4.9</v>
       </c>
       <c r="O94" t="n">
         <v>50</v>
       </c>
       <c r="P94" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q94" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="R94" t="n">
-        <v>-1</v>
+        <v>2.3</v>
       </c>
       <c r="S94" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="T94" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V94" t="n">
         <v>3</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>12.0 (4g)</t>
+          <t>15.0 (5g)</t>
         </is>
       </c>
       <c r="X94" t="n">
-        <v>14.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8079,41 +8087,41 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="F95" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G95" t="n">
-        <v>13.9</v>
+        <v>12.7</v>
       </c>
       <c r="H95" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="I95" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="J95" t="n">
-        <v>25.5</v>
+        <v>24.3</v>
       </c>
       <c r="K95" t="n">
-        <v>27.2</v>
+        <v>26.7</v>
       </c>
       <c r="L95" t="n">
-        <v>43.1</v>
+        <v>34.9</v>
       </c>
       <c r="M95" t="n">
-        <v>44.9</v>
+        <v>43</v>
       </c>
       <c r="N95" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="O95" t="n">
         <v>50</v>
@@ -8122,36 +8130,36 @@
         <v>55</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R95" t="n">
-        <v>-0.9</v>
+        <v>0.4</v>
       </c>
       <c r="S95" t="n">
-        <v>-1.9</v>
+        <v>-8.1</v>
       </c>
       <c r="T95" t="n">
-        <v>-1.7</v>
+        <v>-2.4</v>
       </c>
       <c r="U95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V95" t="n">
         <v>12</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>27.2 (5g)</t>
+          <t>7.8 (4g)</t>
         </is>
       </c>
       <c r="X95" t="n">
-        <v>20.5</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8165,75 +8173,75 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="n">
-        <v>21.3</v>
+        <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
       <c r="G96" t="n">
-        <v>16.3</v>
+        <v>18.6</v>
       </c>
       <c r="H96" t="n">
-        <v>16.6</v>
+        <v>20.3</v>
       </c>
       <c r="I96" t="n">
-        <v>14.5</v>
+        <v>18.2</v>
       </c>
       <c r="J96" t="n">
         <v>31.8</v>
       </c>
       <c r="K96" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="L96" t="n">
-        <v>40.5</v>
+        <v>46</v>
       </c>
       <c r="M96" t="n">
-        <v>39.7</v>
+        <v>49</v>
       </c>
       <c r="N96" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="O96" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P96" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="Q96" t="n">
-        <v>-1</v>
+        <v>5.7</v>
       </c>
       <c r="R96" t="n">
-        <v>2.3</v>
+        <v>-4.4</v>
       </c>
       <c r="S96" t="n">
-        <v>0.8</v>
+        <v>-3</v>
       </c>
       <c r="T96" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="U96" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V96" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>7.2 (5g)</t>
         </is>
       </c>
       <c r="X96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8243,79 +8251,75 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="E97" t="n">
-        <v>14.3</v>
+        <v>22.3</v>
       </c>
       <c r="F97" t="n">
-        <v>14.4</v>
+        <v>16.6</v>
       </c>
       <c r="G97" t="n">
-        <v>12.7</v>
+        <v>17.1</v>
       </c>
       <c r="H97" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="I97" t="n">
-        <v>14</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
-        <v>24.3</v>
+        <v>22.7</v>
       </c>
       <c r="K97" t="n">
-        <v>26.7</v>
+        <v>24</v>
       </c>
       <c r="L97" t="n">
-        <v>34.9</v>
+        <v>41.9</v>
       </c>
       <c r="M97" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="N97" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="O97" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P97" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="S97" t="n">
-        <v>-8.1</v>
+        <v>-1.1</v>
       </c>
       <c r="T97" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="U97" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V97" t="n">
-        <v>12</v>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>7.8 (4g)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="W97" t="inlineStr"/>
       <c r="X97" t="n">
-        <v>-11.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8325,79 +8329,79 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>24.7</v>
       </c>
       <c r="F98" t="n">
-        <v>13.8</v>
+        <v>17.8</v>
       </c>
       <c r="G98" t="n">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="H98" t="n">
-        <v>20.3</v>
+        <v>15.9</v>
       </c>
       <c r="I98" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="J98" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="K98" t="n">
-        <v>32.3</v>
+        <v>29.5</v>
       </c>
       <c r="L98" t="n">
-        <v>46</v>
+        <v>47.2</v>
       </c>
       <c r="M98" t="n">
-        <v>49</v>
+        <v>52.8</v>
       </c>
       <c r="N98" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="O98" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P98" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.7</v>
+        <v>-0.9</v>
       </c>
       <c r="R98" t="n">
-        <v>-4.4</v>
+        <v>3.2</v>
       </c>
       <c r="S98" t="n">
-        <v>-3</v>
+        <v>-5.5</v>
       </c>
       <c r="T98" t="n">
-        <v>-0.5</v>
+        <v>2.2</v>
       </c>
       <c r="U98" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V98" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>7.2 (5g)</t>
+          <t>4.5 (4g)</t>
         </is>
       </c>
       <c r="X98" t="n">
-        <v>8</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8411,75 +8415,71 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>23.5</v>
+        <v>14.5</v>
       </c>
       <c r="E99" t="n">
-        <v>35</v>
+        <v>11.3</v>
       </c>
       <c r="F99" t="n">
-        <v>31.6</v>
+        <v>10.6</v>
       </c>
       <c r="G99" t="n">
-        <v>26.3</v>
+        <v>14.4</v>
       </c>
       <c r="H99" t="n">
-        <v>25.1</v>
+        <v>14.8</v>
       </c>
       <c r="I99" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J99" t="n">
         <v>24.9</v>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L99" t="n">
         <v>36.4</v>
       </c>
-      <c r="K99" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="L99" t="n">
-        <v>46.3</v>
-      </c>
       <c r="M99" t="n">
-        <v>46.6</v>
+        <v>42</v>
       </c>
       <c r="N99" t="n">
-        <v>13.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O99" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P99" t="n">
         <v>50</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="R99" t="n">
-        <v>6.7</v>
+        <v>-4.5</v>
       </c>
       <c r="S99" t="n">
-        <v>-0.3</v>
+        <v>-5.6</v>
       </c>
       <c r="T99" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="U99" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V99" t="n">
-        <v>12</v>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>20.2 (4g)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8489,79 +8489,79 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>26.5</v>
+        <v>10.5</v>
       </c>
       <c r="E100" t="n">
-        <v>26.3</v>
+        <v>10.3</v>
       </c>
       <c r="F100" t="n">
-        <v>24.6</v>
+        <v>11.4</v>
       </c>
       <c r="G100" t="n">
-        <v>23.1</v>
+        <v>14.7</v>
       </c>
       <c r="H100" t="n">
-        <v>26.4</v>
+        <v>13.2</v>
       </c>
       <c r="I100" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="J100" t="n">
-        <v>35.9</v>
+        <v>30.6</v>
       </c>
       <c r="K100" t="n">
-        <v>35.1</v>
+        <v>31.7</v>
       </c>
       <c r="L100" t="n">
-        <v>57</v>
+        <v>57.3</v>
       </c>
       <c r="M100" t="n">
-        <v>56.1</v>
+        <v>51.6</v>
       </c>
       <c r="N100" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="O100" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P100" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>-2.4</v>
+        <v>-0.1</v>
       </c>
       <c r="S100" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="T100" t="n">
-        <v>0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="U100" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V100" t="n">
         <v>12</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>30.6 (5g)</t>
+          <t>12.6 (5g)</t>
         </is>
       </c>
       <c r="X100" t="n">
-        <v>0.2</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8575,55 +8575,55 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>20.5</v>
+        <v>8.5</v>
       </c>
       <c r="E101" t="n">
-        <v>22.3</v>
+        <v>8</v>
       </c>
       <c r="F101" t="n">
-        <v>16.6</v>
+        <v>7.4</v>
       </c>
       <c r="G101" t="n">
-        <v>17.1</v>
+        <v>8.9</v>
       </c>
       <c r="H101" t="n">
-        <v>16.9</v>
+        <v>8.6</v>
       </c>
       <c r="I101" t="n">
-        <v>17.4</v>
+        <v>8.4</v>
       </c>
       <c r="J101" t="n">
-        <v>22.7</v>
+        <v>30.7</v>
       </c>
       <c r="K101" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L101" t="n">
-        <v>41.9</v>
+        <v>43.1</v>
       </c>
       <c r="M101" t="n">
-        <v>42.9</v>
+        <v>38.9</v>
       </c>
       <c r="N101" t="n">
-        <v>8.1</v>
+        <v>4.9</v>
       </c>
       <c r="O101" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P101" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q101" t="n">
-        <v>-3.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R101" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="S101" t="n">
-        <v>-1.1</v>
+        <v>4.2</v>
       </c>
       <c r="T101" t="n">
-        <v>-1.3</v>
+        <v>2.7</v>
       </c>
       <c r="U101" t="n">
         <v>20</v>
@@ -8631,15 +8631,19 @@
       <c r="V101" t="n">
         <v>3</v>
       </c>
-      <c r="W101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>12.0 (4g)</t>
+        </is>
+      </c>
       <c r="X101" t="n">
-        <v>8.4</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8649,79 +8653,79 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="E102" t="n">
+        <v>15</v>
+      </c>
+      <c r="F102" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H102" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I102" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L102" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="N102" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>50</v>
+      </c>
+      <c r="P102" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="S102" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="T102" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="U102" t="n">
         <v>14</v>
       </c>
-      <c r="F102" t="n">
-        <v>14</v>
-      </c>
-      <c r="G102" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I102" t="n">
-        <v>10</v>
-      </c>
-      <c r="J102" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="K102" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L102" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="M102" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="N102" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O102" t="n">
-        <v>90</v>
-      </c>
-      <c r="P102" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="R102" t="n">
-        <v>4</v>
-      </c>
-      <c r="S102" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="T102" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="U102" t="n">
-        <v>11</v>
-      </c>
       <c r="V102" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>8.7 (6g)</t>
+          <t>27.2 (5g)</t>
         </is>
       </c>
       <c r="X102" t="n">
-        <v>14</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8731,79 +8735,79 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15.5</v>
+        <v>23.5</v>
       </c>
       <c r="E103" t="n">
-        <v>24.7</v>
+        <v>35</v>
       </c>
       <c r="F103" t="n">
-        <v>17.8</v>
+        <v>31.6</v>
       </c>
       <c r="G103" t="n">
-        <v>17.4</v>
+        <v>26.3</v>
       </c>
       <c r="H103" t="n">
-        <v>15.9</v>
+        <v>25.1</v>
       </c>
       <c r="I103" t="n">
-        <v>14.6</v>
+        <v>24.9</v>
       </c>
       <c r="J103" t="n">
-        <v>31.7</v>
+        <v>36.4</v>
       </c>
       <c r="K103" t="n">
-        <v>29.5</v>
+        <v>34.9</v>
       </c>
       <c r="L103" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
       <c r="M103" t="n">
-        <v>52.8</v>
+        <v>46.6</v>
       </c>
       <c r="N103" t="n">
-        <v>7.9</v>
+        <v>13.7</v>
       </c>
       <c r="O103" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P103" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q103" t="n">
-        <v>-0.9</v>
+        <v>1.4</v>
       </c>
       <c r="R103" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="S103" t="n">
-        <v>-5.5</v>
+        <v>-0.3</v>
       </c>
       <c r="T103" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="U103" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V103" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>4.5 (4g)</t>
+          <t>20.2 (4g)</t>
         </is>
       </c>
       <c r="X103" t="n">
-        <v>14.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8813,75 +8817,79 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>14.5</v>
+        <v>26.5</v>
       </c>
       <c r="E104" t="n">
-        <v>11.3</v>
+        <v>26.3</v>
       </c>
       <c r="F104" t="n">
-        <v>10.6</v>
+        <v>24.6</v>
       </c>
       <c r="G104" t="n">
-        <v>14.4</v>
+        <v>23.1</v>
       </c>
       <c r="H104" t="n">
-        <v>14.8</v>
+        <v>26.4</v>
       </c>
       <c r="I104" t="n">
-        <v>15.1</v>
+        <v>27</v>
       </c>
       <c r="J104" t="n">
-        <v>24.9</v>
+        <v>35.9</v>
       </c>
       <c r="K104" t="n">
-        <v>23.9</v>
+        <v>35.1</v>
       </c>
       <c r="L104" t="n">
-        <v>36.4</v>
+        <v>57</v>
       </c>
       <c r="M104" t="n">
-        <v>42</v>
+        <v>56.1</v>
       </c>
       <c r="N104" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="O104" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P104" t="n">
         <v>50</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R104" t="n">
-        <v>-4.5</v>
+        <v>-2.4</v>
       </c>
       <c r="S104" t="n">
-        <v>-5.6</v>
+        <v>0.9</v>
       </c>
       <c r="T104" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="U104" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="V104" t="n">
-        <v>3</v>
-      </c>
-      <c r="W104" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>30.6 (5g)</t>
+        </is>
+      </c>
       <c r="X104" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8895,37 +8903,37 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E105" t="n">
-        <v>10.3</v>
+        <v>14</v>
       </c>
       <c r="F105" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="G105" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H105" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="I105" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J105" t="n">
-        <v>30.6</v>
+        <v>23.4</v>
       </c>
       <c r="K105" t="n">
-        <v>31.7</v>
+        <v>18.5</v>
       </c>
       <c r="L105" t="n">
-        <v>57.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M105" t="n">
-        <v>51.6</v>
+        <v>54.4</v>
       </c>
       <c r="N105" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="O105" t="n">
         <v>90</v>
@@ -8934,30 +8942,30 @@
         <v>75</v>
       </c>
       <c r="Q105" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="R105" t="n">
-        <v>-0.1</v>
+        <v>4</v>
       </c>
       <c r="S105" t="n">
-        <v>5.8</v>
+        <v>15.7</v>
       </c>
       <c r="T105" t="n">
-        <v>-1.1</v>
+        <v>4.9</v>
       </c>
       <c r="U105" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V105" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>12.6 (5g)</t>
+          <t>8.7 (6g)</t>
         </is>
       </c>
       <c r="X105" t="n">
-        <v>-5.8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9076,10 +9084,10 @@
         <v>8.1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.893</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.833</v>
+        <v>1.345</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -9109,10 +9117,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.636</v>
+        <v>0.708</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9121,17 +9129,17 @@
         <v>7.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.962</v>
+        <v>2.3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.769</v>
+        <v>1.345</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Dieng has a H2H avg of 3.0 pts vs this opponent (-8.5 vs line) — supporting the UNDER. His H2H avg of 3.0 pts is 4.5 below his season L30; His TS% shifts +13.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#27). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 7.1 pts (4.4 pts below line; 63% blended confidence). Risk: L3 has surged to 11.7 after a 17-pt performance (4.2 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Dieng has a H2H avg of 3.0 pts vs this opponent (-10.5 vs line) — supporting the UNDER. His H2H avg of 3.0 pts is 4.5 below his season L30; His TS% shifts +13.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#27). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, FG Trend dissent. Projection model targets 7.1 pts (6.4 pts below line; 70% blended confidence). Risk: L3 has surged to 11.7 after a 17-pt performance (4.2 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -9172,10 +9180,10 @@
         <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1.917</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.82</v>
+        <v>1.345</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -9220,10 +9228,10 @@
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -9244,38 +9252,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.504</v>
+        <v>0.548</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.926</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1.806</v>
+        <v>1.364</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Leonard has a H2H avg of 23.7 pts vs this opponent (-4.8 vs line) — supporting the lean UNDER. His H2H avg of 23.7 pts is 5.1 below his season L30; His TS% shifts -4.3% in this matchup. Opponent ranks as weak defense (#23) with moderate pace (#13). 5/10 signals agree — HR L30, HR L10, Trend support under; Volume, Defense against. Projection model targets 28.6 pts (0.1 pts above line; 50% blended confidence).</t>
+          <t>Leonard has a H2H avg of 23.7 pts vs this opponent (-3.8 vs line) — working against the OVER. His H2H avg of 23.7 pts is 5.1 below his season L30; His TS% shifts -4.3% in this matchup. Opponent ranks as weak defense (#23) with moderate pace (#13). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 28.4 pts (0.9 pts above line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9316,10 +9324,10 @@
         <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.952</v>
+        <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>1.787</v>
+        <v>1.385</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -9349,7 +9357,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.591</v>
+        <v>0.602</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -9361,17 +9369,17 @@
         <v>7.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.847</v>
+        <v>2.02</v>
       </c>
       <c r="K8" t="n">
-        <v>1.885</v>
+        <v>1.73</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Collins shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). FG% trend -14.3% (L10 vs L30). Opponent ranks as weak defense (#23) with moderate pace (#13). Mixed signal picture: 3/10 agree. Agreeing: Trend, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.4 pts (2.1 pts below line; 59% blended confidence). Risk: 85% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Collins shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). FG% trend -14.3% (L10 vs L30). Opponent ranks as weak defense (#23) with moderate pace (#13). Mixed signal picture: 3/10 agree. Agreeing: Trend, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.4 pts (3.1 pts below line; 60% blended confidence). Risk: 80% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
@@ -9393,33 +9401,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.616</v>
+        <v>0.596</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.885</v>
+        <v>2.65</v>
       </c>
       <c r="K9" t="n">
-        <v>1.847</v>
+        <v>1.455</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Lopez shows recent scoring up 2.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#3) with moderate pace (#13). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, H2H dissent. Projection model targets 14.2 pts (4.7 pts above line; 61% blended confidence).</t>
+          <t>Lopez shows recent scoring up 2.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#3) with moderate pace (#13). Mixed signal picture: 4/10 agree. Agreeing: Trend, Context, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.1 pts (3.6 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9460,10 +9468,10 @@
         <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.826</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.909</v>
+        <v>1.385</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -9508,10 +9516,10 @@
         <v>7.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.806</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1.926</v>
+        <v>1.435</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -9556,10 +9564,10 @@
         <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.787</v>
+        <v>2.85</v>
       </c>
       <c r="K12" t="n">
-        <v>1.952</v>
+        <v>1.4</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -9580,19 +9588,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.545</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -9601,24 +9609,24 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.926</v>
+        <v>2.65</v>
       </c>
       <c r="K13" t="n">
-        <v>1.806</v>
+        <v>1.455</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Ware shows low scoring variance (σ=4.6) — highly predictable output. His TS% shifts +19.0% in this matchup. Opponent ranks as weak defense (#24) with moderate pace (#14). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, FG Trend dissent. Projection model targets 8.3 pts (0.2 pts below line; 54% blended confidence).</t>
+          <t>Ware shows low scoring variance (σ=4.6) — highly predictable output. His TS% shifts +19.0% in this matchup. Opponent ranks as weak defense (#24) with moderate pace (#14). Mixed signal picture: 3/10 agree. Agreeing: Trend, Context, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.3 pts (1.2 pts below line; 56% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9637,7 +9645,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.605</v>
+        <v>0.627</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -9646,27 +9654,27 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>15.1</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.952</v>
+        <v>2.55</v>
       </c>
       <c r="K14" t="n">
-        <v>1.775</v>
+        <v>1.476</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Powell has a H2H avg of 17.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 17.0 pts is 3.7 below his season L30; His TS% shifts -16.7% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). Mixed signal picture: 4/10 agree. Agreeing: Trend, H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 15.1 pts (4.4 pts below line; 60% blended confidence).</t>
+          <t>Mitchell has a H2H avg of 6.0 pts vs this opponent (-3.5 vs line) — supporting the UNDER. His H2H avg of 6.0 pts is 2.4 below his season L30; His TS% shifts -11.4% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 4.3 pts (5.2 pts below line; 62% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9685,36 +9693,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.612</v>
+        <v>0.573</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>11.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="K15" t="n">
-        <v>1.855</v>
+        <v>1.417</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Mitchell has a H2H avg of 6.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 6.0 pts is 2.4 below his season L30; His TS% shifts -11.4% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 4.3 pts (4.2 pts below line; 61% blended confidence).</t>
+          <t>Walker has a H2H avg of 7.5 pts vs this opponent (-6.0 vs line) — supporting the UNDER. His H2H avg of 7.5 pts is 7.6 below his season L30; His TS% shifts +9.6% in this matchup. Opponent ranks as weak defense (#23) with fast pace (#4). Mixed signal picture: 2/10 agree. Agreeing: Trend, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 11.4 pts (2.1 pts below line; 57% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9733,29 +9741,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.758</v>
+        <v>1.84</v>
       </c>
       <c r="K16" t="n">
-        <v>1.98</v>
+        <v>1.917</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Walker has a H2H avg of 7.5 pts vs this opponent (-5.0 vs line) — supporting the UNDER. His H2H avg of 7.5 pts is 7.6 below his season L30; His TS% shifts +9.6% in this matchup. Opponent ranks as weak defense (#23) with fast pace (#4). Mixed signal picture: 2/10 agree. Agreeing: Trend, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 11.4 pts (1.1 pts below line; 55% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Larsson has a H2H avg of 6.7 pts vs this opponent (-5.8 vs line) — supporting the UNDER. His H2H avg of 6.7 pts is 6.3 below his season L30; His TS% shifts +18.3% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). 5/10 signals agree — HR L30, Trend, Context support under; Volume, HR L10 against. Projection model targets 10.9 pts (1.6 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9796,10 +9804,10 @@
         <v>2.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.769</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>1.98</v>
+        <v>1.345</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -9844,10 +9852,10 @@
         <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.952</v>
+        <v>2.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1.775</v>
+        <v>1.435</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -9892,10 +9900,10 @@
         <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.855</v>
+        <v>2.85</v>
       </c>
       <c r="K19" t="n">
-        <v>1.877</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -9925,10 +9933,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.616</v>
+        <v>0.583</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9937,17 +9945,17 @@
         <v>25.6</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.909</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>1.826</v>
+        <v>1.333</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Adebayo shows recent scoring down 2.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 21.0 pts is 2.9 below his season L30; His TS% shifts +8.7% in this matchup. Opponent ranks as weak defense (#24) with moderate pace (#14). 6/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 25.6 pts (4.1 pts above line; 61% blended confidence). Risk: L3 has dropped to 16.3 (7.6 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Adebayo shows recent scoring down 2.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 21.0 pts is 2.9 below his season L30; His TS% shifts +8.7% in this matchup. Opponent ranks as weak defense (#24) with moderate pace (#14). 5/10 signals agree — Volume, Context, Defense support over; HR L30, HR L10 against. Projection model targets 25.6 pts (3.1 pts above line; 58% blended confidence). Risk: L3 has dropped to 16.3 (7.6 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
@@ -9969,33 +9977,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.515</v>
+        <v>0.579</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="K21" t="n">
-        <v>1.917</v>
+        <v>1.435</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Herro shows recent scoring down 2.6 pts vs L30 (L5 vs L30 trend). His H2H avg of 23.0 pts is 1.8 above his season L30; His TS% shifts -3.3% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). Mixed signal picture: 3/10 agree. Agreeing: Trend, Context, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 20.2 pts (0.3 pts below line; 51% blended confidence).</t>
+          <t>Herro shows recent scoring down 2.6 pts vs L30 (L5 vs L30 trend). His H2H avg of 23.0 pts is 1.8 above his season L30; His TS% shifts -3.3% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 20.0 pts (2.5 pts below line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -10036,10 +10044,10 @@
         <v>3.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1.917</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.82</v>
+        <v>1.357</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -10050,7 +10058,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10069,46 +10077,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.631</v>
+        <v>0.583</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.962</v>
+        <v>1.877</v>
       </c>
       <c r="K23" t="n">
-        <v>1.769</v>
+        <v>1.877</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Nesmith has a H2H avg of 9.3 pts vs this opponent (-4.2 vs line) — supporting the UNDER. His H2H avg of 9.3 pts is 4.4 below his season L30; His TS% shifts -13.7% in this matchup. Opponent ranks as below-average defense (#22) with fast pace (#4). Mixed signal picture: 2/10 agree. Agreeing: Context, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.7 pts (4.8 pts below line; 63% blended confidence). Risk: L3 has surged to 19.7 after a 18-pt performance (6.0 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Jr. has a H2H avg of 11.2 pts vs this opponent (-3.3 vs line) — supporting the UNDER. His H2H avg of 11.2 pts is 2.6 below his season L30; His TS% shifts +7.3% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#14). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 11.3 pts (3.2 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOS @ CHA</t>
+          <t>MIA @ IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10117,36 +10125,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.669</v>
+        <v>0.605</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>27.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>1.735</v>
+        <v>1.333</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Ball has a H2H avg of 28.3 pts vs this opponent (+7.8 vs line) — supporting the OVER. His H2H avg of 28.3 pts is 8.2 above his season L30; His TS% shifts +7.3% in this matchup. Opponent ranks as elite defense (#2) with slow pace (#24). 5/10 signals agree — Trend, Context, H2H support over; Volume, HR L30 against. Projection model targets 27.5 pts (7.0 pts above line; 66% blended confidence). Risk: only 40% hit rate over L30 — line may be set fairly.</t>
+          <t>Nesmith has a H2H avg of 9.3 pts vs this opponent (-2.2 vs line) — supporting the UNDER. His H2H avg of 9.3 pts is 4.4 below his season L30; His TS% shifts -13.7% in this matchup. Opponent ranks as below-average defense (#22) with fast pace (#4). Mixed signal picture: 1/10 agree. Agreeing: H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.7 pts (2.8 pts below line; 60% blended confidence). Risk: L3 has surged to 19.7 after a 18-pt performance (6.0 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10161,40 +10169,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_ULTRA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.541</v>
+        <v>0.72</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>19.4</v>
+        <v>27.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.952</v>
+        <v>2.9</v>
       </c>
       <c r="K25" t="n">
-        <v>1.82</v>
+        <v>1.385</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Pritchard shows recent scoring up 2.4 pts vs L30 (L5 vs L30 trend). His TS% shifts +6.4% in this matchup. Opponent ranks as strong defense (#9) with moderate pace (#17). 6/10 signals agree — HR L30, HR L10, Trend support over; Volume, Defense against. Projection model targets 19.4 pts (1.9 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=8.2) introduces outcome uncertainty.</t>
+          <t>Ball has a H2H avg of 28.3 pts vs this opponent (+8.8 vs line) — supporting the OVER. His H2H avg of 28.3 pts is 8.2 above his season L30; His TS% shifts +7.3% in this matchup. Opponent ranks as elite defense (#2) with slow pace (#24). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 27.6 pts (8.1 pts above line; 71% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10213,7 +10221,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.577</v>
+        <v>0.521</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -10222,27 +10230,27 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>18.2</v>
+        <v>19.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.855</v>
+        <v>2.75</v>
       </c>
       <c r="K26" t="n">
-        <v>1.917</v>
+        <v>1.417</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>White has a H2H avg of 20.8 pts vs this opponent (+5.3 vs line) — supporting the OVER. His H2H avg of 20.8 pts is 5.0 above his season L30; His TS% shifts +4.1% in this matchup. Opponent ranks as strong defense (#9) with moderate pace (#17). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 18.2 pts (2.7 pts above line; 57% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
+          <t>Pritchard shows recent scoring up 2.4 pts vs L30 (L5 vs L30 trend). His TS% shifts +6.4% in this matchup. Opponent ranks as strong defense (#9) with moderate pace (#17). Mixed signal picture: 3/10 agree. Agreeing: Trend, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 19.4 pts (0.9 pts above line; 52% blended confidence). Risk: high scoring volatility (σ=8.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10252,45 +10260,45 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>19.3</v>
+        <v>18.4</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1.901</v>
+        <v>2.75</v>
       </c>
       <c r="K27" t="n">
-        <v>1.877</v>
+        <v>1.417</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Tatum shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). His H2H avg of 25.7 pts is 1.6 above his season L30; FG% trend -3.6% (L10 vs L30). Opponent ranks as strong defense (#8) with moderate pace (#17). 6/10 signals agree — HR L10, Trend, Defense support under; Volume, HR L30 against. Projection model targets 19.3 pts (2.2 pts below line; 55% blended confidence). Risk: minutes trending down (31.0 L10 vs 34.7 L30 — role reduction would suppress counting stats.</t>
+          <t>White has a H2H avg of 20.8 pts vs this opponent (+3.3 vs line) — supporting the OVER. His H2H avg of 20.8 pts is 5.0 above his season L30; His TS% shifts +4.1% in this matchup. Opponent ranks as strong defense (#9) with moderate pace (#17). Mixed signal picture: 1/10 agree. Agreeing: H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 18.4 pts (0.9 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10300,38 +10308,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.52</v>
+        <v>0.626</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>19.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1.758</v>
+        <v>2.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.408</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Williams shows recent scoring down 3.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#2) with slow pace (#24). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 4.3 pts (0.2 pts below line; 51% blended confidence).</t>
+          <t>Tatum shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). His H2H avg of 25.7 pts is 1.6 above his season L30; FG% trend -3.6% (L10 vs L30). Opponent ranks as strong defense (#8) with moderate pace (#17). 8/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, H2H dissent. Projection model targets 19.3 pts (4.2 pts below line; 62% blended confidence). Risk: minutes trending down (31.0 L10 vs 34.7 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -10372,10 +10380,10 @@
         <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1.962</v>
+        <v>1.364</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -10420,10 +10428,10 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1.775</v>
+        <v>1.909</v>
       </c>
       <c r="K30" t="n">
-        <v>2.01</v>
+        <v>1.862</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -10468,10 +10476,10 @@
         <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1.833</v>
+        <v>1.952</v>
       </c>
       <c r="K31" t="n">
-        <v>1.909</v>
+        <v>1.8</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10524,10 @@
         <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="K32" t="n">
-        <v>1.758</v>
+        <v>1.455</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -10549,10 +10557,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.575</v>
+        <v>0.61</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -10561,17 +10569,17 @@
         <v>6.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
-        <v>1.952</v>
+        <v>2.8</v>
       </c>
       <c r="K33" t="n">
-        <v>1.826</v>
+        <v>1.408</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Queta has a H2H avg of 5.4 pts vs this opponent (-3.1 vs line) — supporting the UNDER. His H2H avg of 5.4 pts is 3.9 below his season L30; His TS% shifts -4.7% in this matchup. Opponent ranks as elite defense (#4) with moderate pace (#17). 8/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, Min Trend dissent. Projection model targets 6.2 pts (2.3 pts below line; 57% blended confidence).</t>
+          <t>Queta has a H2H avg of 5.4 pts vs this opponent (-4.1 vs line) — supporting the UNDER. His H2H avg of 5.4 pts is 3.9 below his season L30; His TS% shifts -4.7% in this matchup. Opponent ranks as elite defense (#4) with moderate pace (#17). 9/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Min Trend dissents. Projection model targets 6.2 pts (3.3 pts below line; 60% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -10612,10 +10620,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>1.877</v>
+        <v>2.7</v>
       </c>
       <c r="K34" t="n">
-        <v>1.893</v>
+        <v>1.435</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -10636,7 +10644,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10645,10 +10653,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.54</v>
+        <v>0.536</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -10657,24 +10665,24 @@
         <v>18.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K35" t="n">
-        <v>1.893</v>
+        <v>1.385</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Knueppel shows recent scoring down 3.5 pts vs L30 (L5 vs L30 trend). FG% trend -3.7% (L10 vs L30). Opponent ranks as elite defense (#2) with slow pace (#24). 7/10 signals agree (HR L10, Trend, Context, Defense among the strongest); Volume, HR L30 dissent. Projection model targets 18.1 pts (0.4 pts below line; 54% blended confidence).</t>
+          <t>Knueppel shows recent scoring down 3.5 pts vs L30 (L5 vs L30 trend). FG% trend -3.7% (L10 vs L30). Opponent ranks as elite defense (#2) with slow pace (#24). Mixed signal picture: 3/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 18.1 pts (0.6 pts above line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10693,29 +10701,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.624</v>
+        <v>0.535</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>21.7</v>
+        <v>9.1</v>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="K36" t="n">
         <v>1.935</v>
       </c>
-      <c r="K36" t="n">
-        <v>1.84</v>
-      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Brown shows recent scoring up 5.2 pts vs L30 (L5 vs L30 trend). Opponent ranks as strong defense (#9) with moderate pace (#17). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 21.7 pts (4.8 pts below line; 62% blended confidence). Risk: high scoring volatility (σ=9.5) introduces outcome uncertainty.</t>
+          <t>Hauser shows recent scoring down 4.1 pts vs L30 (L5 vs L30 trend). His TS% shifts +11.8% in this matchup; FG% trend -5.6% (L10 vs L30). Opponent ranks as strong defense (#8) with moderate pace (#17). 8/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, H2H dissent. Projection model targets 9.1 pts (0.4 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -10756,10 +10764,10 @@
         <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="K37" t="n">
-        <v>1.901</v>
+        <v>1.4</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -10804,10 +10812,10 @@
         <v>5.4</v>
       </c>
       <c r="J38" t="n">
-        <v>1.962</v>
+        <v>2.85</v>
       </c>
       <c r="K38" t="n">
-        <v>1.813</v>
+        <v>1.4</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -10837,10 +10845,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.672</v>
+        <v>0.633</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -10849,17 +10857,17 @@
         <v>22.4</v>
       </c>
       <c r="I39" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>1.787</v>
+        <v>1.333</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Raynaud shows recent scoring up 4.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#19) with slow pace (#30). 6/10 signals agree — HR L30, HR L10, Trend support over; Volume, Context against. Projection model targets 22.4 pts (6.9 pts above line; 67% blended confidence). Risk: high scoring volatility (σ=9.1) introduces outcome uncertainty.</t>
+          <t>Raynaud shows recent scoring up 4.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#19) with slow pace (#30). 5/10 signals agree — HR L10, Trend, Defense support over; Volume, HR L30 against. Projection model targets 22.4 pts (5.9 pts above line; 63% blended confidence). Risk: high scoring volatility (σ=9.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10900,10 +10908,10 @@
         <v>0.3</v>
       </c>
       <c r="J40" t="n">
-        <v>1.794</v>
+        <v>2.7</v>
       </c>
       <c r="K40" t="n">
-        <v>1.98</v>
+        <v>1.435</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -10948,10 +10956,10 @@
         <v>6.8</v>
       </c>
       <c r="J41" t="n">
-        <v>1.769</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>2.02</v>
+        <v>1.364</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -10996,10 +11004,10 @@
         <v>1.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="K42" t="n">
-        <v>1.769</v>
+        <v>1.385</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -11044,10 +11052,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="K43" t="n">
-        <v>1.962</v>
+        <v>1.417</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -11092,10 +11100,10 @@
         <v>4.3</v>
       </c>
       <c r="J44" t="n">
-        <v>1.847</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>1.926</v>
+        <v>1.345</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -11140,10 +11148,10 @@
         <v>0.4</v>
       </c>
       <c r="J45" t="n">
-        <v>1.847</v>
+        <v>2.7</v>
       </c>
       <c r="K45" t="n">
-        <v>1.926</v>
+        <v>1.435</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -11188,10 +11196,10 @@
         <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>1.909</v>
+        <v>2.75</v>
       </c>
       <c r="K46" t="n">
-        <v>1.847</v>
+        <v>1.417</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -11236,10 +11244,10 @@
         <v>3.6</v>
       </c>
       <c r="J47" t="n">
-        <v>1.98</v>
+        <v>3.15</v>
       </c>
       <c r="K47" t="n">
-        <v>1.787</v>
+        <v>1.333</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -11269,10 +11277,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.599</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -11281,17 +11289,17 @@
         <v>13.6</v>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>1.893</v>
+        <v>1.364</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Silva shows recent scoring up 4.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +18.7% in this matchup; FG% trend +3.7% (L10 vs L30). Opponent ranks as strong defense (#6) with slow pace (#25). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, H2H dissent. Projection model targets 13.6 pts (3.1 pts above line; 59% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
+          <t>Silva shows recent scoring up 4.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +18.7% in this matchup; FG% trend +3.7% (L10 vs L30). Opponent ranks as strong defense (#6) with slow pace (#25). 6/10 signals agree — HR L30, HR L10, Trend support over; Volume, Defense against. Projection model targets 13.6 pts (2.1 pts above line; 56% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -11332,10 +11340,10 @@
         <v>3.7</v>
       </c>
       <c r="J49" t="n">
-        <v>1.699</v>
+        <v>3.05</v>
       </c>
       <c r="K49" t="n">
-        <v>2.1</v>
+        <v>1.357</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -11380,10 +11388,10 @@
         <v>5.2</v>
       </c>
       <c r="J50" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K50" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -11428,10 +11436,10 @@
         <v>3.6</v>
       </c>
       <c r="J51" t="n">
-        <v>1.82</v>
+        <v>3.15</v>
       </c>
       <c r="K51" t="n">
-        <v>1.943</v>
+        <v>1.333</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -11476,10 +11484,10 @@
         <v>4.3</v>
       </c>
       <c r="J52" t="n">
-        <v>1.847</v>
+        <v>2.9</v>
       </c>
       <c r="K52" t="n">
-        <v>1.909</v>
+        <v>1.385</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -11509,7 +11517,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.536</v>
+        <v>0.553</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -11521,17 +11529,17 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="K53" t="n">
-        <v>1.971</v>
+        <v>1.345</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Walter shows recent scoring up 5.7 pts vs L30 (L5 vs L30 trend). His TS% shifts +16.7% in this matchup; FG% trend +11.8% (L10 vs L30). Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 8.8 pts (0.7 pts below line; 53% blended confidence). Risk: L3 has surged to 14.7 after a 6-pt performance (6.2 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Walter shows recent scoring up 5.7 pts vs L30 (L5 vs L30 trend). His TS% shifts +16.7% in this matchup; FG% trend +11.8% (L10 vs L30). Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 8.8 pts (1.7 pts below line; 55% blended confidence). Risk: L3 has surged to 14.7 after a 6-pt performance (6.2 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -11572,10 +11580,10 @@
         <v>0.2</v>
       </c>
       <c r="J54" t="n">
-        <v>1.952</v>
+        <v>3.05</v>
       </c>
       <c r="K54" t="n">
-        <v>1.813</v>
+        <v>1.357</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -11605,29 +11613,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.543</v>
+        <v>0.521</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
-        <v>1.813</v>
+        <v>2.75</v>
       </c>
       <c r="K55" t="n">
-        <v>1.962</v>
+        <v>1.417</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Poeltl has a H2H avg of 16.5 pts vs this opponent (+6.0 vs line) — supporting the OVER. His H2H avg of 16.5 pts is 5.4 above his season L30; His TS% shifts +13.9% in this matchup. Opponent ranks as average defense (#11) with slow pace (#29). 5/10 signals agree — Volume, Trend, Context support over; HR L30, HR L10 against. Projection model targets 12.2 pts (1.7 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=7.3) introduces outcome uncertainty.</t>
+          <t>Poeltl has a H2H avg of 16.5 pts vs this opponent (+5.0 vs line) — supporting the OVER. His H2H avg of 16.5 pts is 5.4 above his season L30; His TS% shifts +13.9% in this matchup. Opponent ranks as average defense (#11) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Trend, Context, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 12.0 pts (0.5 pts above line; 52% blended confidence). Risk: high scoring volatility (σ=7.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -11668,10 +11676,10 @@
         <v>0.9</v>
       </c>
       <c r="J56" t="n">
-        <v>1.917</v>
+        <v>2.85</v>
       </c>
       <c r="K56" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -11682,7 +11690,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11701,36 +11709,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.525</v>
+        <v>0.584</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="I57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K57" t="n">
         <v>1.4</v>
       </c>
-      <c r="J57" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1.833</v>
-      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Camara shows recent scoring up 2.1 pts vs L30 (L5 vs L30 trend). FG% trend +4.0% (L10 vs L30). Opponent ranks as weak defense (#30) with above-average pace (#11). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 13.1 pts (1.4 pts below line; 52% blended confidence). Risk: L3 has surged to 17.7 after a 14-pt performance (4.8 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Coulibaly shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#20) with moderate pace (#19). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 10.1 pts (2.4 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11745,40 +11753,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>15.1</v>
+        <v>11.8</v>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J58" t="n">
-        <v>1.794</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1.99</v>
+        <v>1.357</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Henderson's L30 average of 12.8 pts is 3.7 below the 16.5 line, supports the UNDER. FG% trend +4.9% (L10 vs L30). Opponent ranks as weak defense (#24) with above-average pace (#11). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, HR L10. Counter-signals: Trend, Defense, H2H. Projection model targets 15.1 pts (1.4 pts below line; 55% blended confidence).</t>
+          <t>Clingan has a H2H avg of 9.7 pts vs this opponent (-6.8 vs line) — supporting the UNDER. His H2H avg of 9.7 pts is 3.9 below his season L30; His TS% shifts -13.2% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#11). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 11.8 pts (4.7 pts below line; 62% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11793,40 +11801,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.695</v>
+        <v>0.525</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="I59" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
-        <v>1.833</v>
+        <v>2.85</v>
       </c>
       <c r="K59" t="n">
-        <v>1.909</v>
+        <v>1.4</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Holiday has a H2H avg of 10.6 pts vs this opponent (-6.9 vs line) — supporting the UNDER. His H2H avg of 10.6 pts is 5.8 below his season L30; His TS% shifts -6.2% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#11). 6/10 signals agree — Volume, HR L10, Trend support under; HR L30, Defense against. Projection model targets 10.6 pts (6.9 pts below line; 69% blended confidence).</t>
+          <t>Camara shows recent scoring up 2.1 pts vs L30 (L5 vs L30 trend). FG% trend +4.0% (L10 vs L30). Opponent ranks as weak defense (#30) with above-average pace (#11). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 13.1 pts (1.4 pts below line; 52% blended confidence). Risk: L3 has surged to 17.7 after a 14-pt performance (4.8 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sidy Cissoko</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11841,40 +11849,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.74</v>
+        <v>0.537</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1</v>
+        <v>11.4</v>
       </c>
       <c r="I60" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>1.741</v>
+        <v>1.357</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Cissoko shows low scoring variance (σ=4.5) — highly predictable output. FG% trend -3.9% (L10 vs L30). Opponent ranks as weak defense (#24) with above-average pace (#11). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, H2H dissent. Projection model targets -0.1 pts (7.6 pts below line; 73% blended confidence). Risk: minutes trending down (14.0 L10 vs 19.2 L30 — role reduction would suppress counting stats.</t>
+          <t>Vukcevic's L30 average of 10.7 pts vs line of 12.5, supports the UNDER. Opponent ranks as below-average defense (#20) with moderate pace (#19). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 11.4 pts (1.1 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11889,40 +11897,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.794</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>12.8</v>
+        <v>15.1</v>
       </c>
       <c r="I61" t="n">
-        <v>13.7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
-        <v>1.885</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>1.885</v>
+        <v>1.364</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Avdija has a H2H avg of 12.3 pts vs this opponent (-14.2 vs line) — supporting the UNDER. His H2H avg of 12.3 pts is 10.0 below his season L30; His TS% shifts -3.9% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, Pace against. Projection model targets 12.8 pts (13.7 pts below line; 79% blended confidence).</t>
+          <t>Henderson's L30 average of 12.8 pts is 3.7 below the 16.5 line, supports the UNDER. FG% trend +4.9% (L10 vs L30). Opponent ranks as weak defense (#24) with above-average pace (#11). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, HR L10. Counter-signals: Trend, Defense, H2H. Projection model targets 15.1 pts (1.4 pts below line; 55% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11941,36 +11949,36 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.584</v>
+        <v>0.654</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J62" t="n">
-        <v>1.862</v>
+        <v>2.9</v>
       </c>
       <c r="K62" t="n">
-        <v>1.909</v>
+        <v>1.385</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Coulibaly shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#20) with moderate pace (#19). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 10.1 pts (2.4 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
+          <t>Riley's L30 average of 13.9 pts vs line of 16.5, supports the UNDER. FG% trend -3.3% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#19). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 10.6 pts (5.9 pts below line; 65% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11985,40 +11993,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.653</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>11.9</v>
+        <v>5.7</v>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
-        <v>1.847</v>
+        <v>2.85</v>
       </c>
       <c r="K63" t="n">
-        <v>1.926</v>
+        <v>1.4</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Clingan has a H2H avg of 9.7 pts vs this opponent (-7.8 vs line) — supporting the UNDER. His H2H avg of 9.7 pts is 3.9 below his season L30; His TS% shifts -13.2% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#11). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 11.9 pts (5.6 pts below line; 65% blended confidence).</t>
+          <t>III's L30 average of 7.2 pts vs line of 8.5, supports the UNDER. FG% trend -9.3% (L10 vs L30). Opponent ranks as weak defense (#30) with above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 5.7 pts (2.8 pts below line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12033,40 +12041,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.537</v>
+        <v>0.695</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J64" t="n">
-        <v>1.806</v>
+        <v>1.87</v>
       </c>
       <c r="K64" t="n">
-        <v>1.971</v>
+        <v>1.87</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Vukcevic's L30 average of 10.7 pts vs line of 12.5, supports the UNDER. Opponent ranks as below-average defense (#20) with moderate pace (#19). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 11.4 pts (1.1 pts below line; 53% blended confidence).</t>
+          <t>Holiday has a H2H avg of 10.6 pts vs this opponent (-6.9 vs line) — supporting the UNDER. His H2H avg of 10.6 pts is 5.8 below his season L30; His TS% shifts -6.2% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#11). 6/10 signals agree — Volume, HR L10, Trend support under; HR L30, Defense against. Projection model targets 10.6 pts (6.9 pts below line; 69% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Sidy Cissoko</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12081,40 +12089,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.654</v>
+        <v>0.74</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>10.6</v>
+        <v>-0.1</v>
       </c>
       <c r="I65" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J65" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>1.901</v>
+        <v>1.364</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Riley's L30 average of 13.9 pts vs line of 16.5, supports the UNDER. FG% trend -3.3% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#19). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 10.6 pts (5.9 pts below line; 65% blended confidence).</t>
+          <t>Cissoko shows low scoring variance (σ=4.5) — highly predictable output. FG% trend -3.9% (L10 vs L30). Opponent ranks as weak defense (#24) with above-average pace (#11). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, H2H dissent. Projection model targets -0.1 pts (7.6 pts below line; 73% blended confidence). Risk: minutes trending down (14.0 L10 vs 19.2 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -12133,7 +12141,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="F66" t="n">
         <v>6</v>
@@ -12142,20 +12150,20 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>5.7</v>
+        <v>12.8</v>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>13.7</v>
       </c>
       <c r="J66" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="K66" t="n">
-        <v>1.775</v>
+        <v>1.385</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>III's L30 average of 7.2 pts vs line of 8.5, supports the UNDER. FG% trend -9.3% (L10 vs L30). Opponent ranks as weak defense (#30) with above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 5.7 pts (2.8 pts below line; 56% blended confidence).</t>
+          <t>Avdija has a H2H avg of 12.3 pts vs this opponent (-14.2 vs line) — supporting the UNDER. His H2H avg of 12.3 pts is 10.0 below his season L30; His TS% shifts -3.9% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, Pace against. Projection model targets 12.8 pts (13.7 pts below line; 79% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -12196,10 +12204,10 @@
         <v>0.7</v>
       </c>
       <c r="J67" t="n">
-        <v>1.833</v>
+        <v>3.1</v>
       </c>
       <c r="K67" t="n">
-        <v>1.893</v>
+        <v>1.345</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -12225,33 +12233,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.627</v>
+        <v>0.664</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>9.5</v>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>1.877</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>1.855</v>
+        <v>1.364</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Sheppard has a H2H avg of 7.5 pts vs this opponent (-7.0 vs line) — supporting the UNDER. His H2H avg of 7.5 pts is 6.6 below his season L30; His TS% shifts -10.2% in this matchup. Opponent ranks as weak defense (#23) with above-average pace (#8). 5/10 signals agree — Volume, HR L10, Context support under; HR L30, Trend against. Projection model targets 9.5 pts (5.0 pts below line; 62% blended confidence).</t>
+          <t>Sheppard has a H2H avg of 7.5 pts vs this opponent (-8.0 vs line) — supporting the UNDER. His H2H avg of 7.5 pts is 6.6 below his season L30; His TS% shifts -10.2% in this matchup. Opponent ranks as weak defense (#23) with above-average pace (#8). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 9.5 pts (6.0 pts below line; 66% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -12292,10 +12300,10 @@
         <v>0.2</v>
       </c>
       <c r="J69" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K69" t="n">
-        <v>1.943</v>
+        <v>1.408</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -12340,10 +12348,10 @@
         <v>0.8</v>
       </c>
       <c r="J70" t="n">
-        <v>1.719</v>
+        <v>2.75</v>
       </c>
       <c r="K70" t="n">
-        <v>2.05</v>
+        <v>1.417</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -12388,10 +12396,10 @@
         <v>4.3</v>
       </c>
       <c r="J71" t="n">
-        <v>1.787</v>
+        <v>2.9</v>
       </c>
       <c r="K71" t="n">
-        <v>1.943</v>
+        <v>1.385</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
@@ -12436,10 +12444,10 @@
         <v>2.9</v>
       </c>
       <c r="J72" t="n">
-        <v>1.962</v>
+        <v>3.05</v>
       </c>
       <c r="K72" t="n">
-        <v>1.775</v>
+        <v>1.357</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -12484,10 +12492,10 @@
         <v>0.1</v>
       </c>
       <c r="J73" t="n">
-        <v>1.885</v>
+        <v>3.05</v>
       </c>
       <c r="K73" t="n">
-        <v>1.87</v>
+        <v>1.357</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -12532,10 +12540,10 @@
         <v>0.1</v>
       </c>
       <c r="J74" t="n">
-        <v>1.833</v>
+        <v>2.6</v>
       </c>
       <c r="K74" t="n">
-        <v>1.893</v>
+        <v>1.465</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
@@ -12565,10 +12573,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.598</v>
+        <v>0.606</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -12577,17 +12585,17 @@
         <v>16.1</v>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
-        <v>1.909</v>
+        <v>2.9</v>
       </c>
       <c r="K75" t="n">
-        <v>1.826</v>
+        <v>1.385</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Williamson shows low scoring variance (σ=4.0) — highly predictable output. His H2H avg of 18.0 pts is 2.2 below his season L30; His TS% shifts -8.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#21). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 16.1 pts (3.4 pts below line; 59% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Williamson has a H2H avg of 18.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 18.0 pts is 2.2 below his season L30; His TS% shifts -8.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#21). 5/10 signals agree — Volume, Context, Defense support under; HR L30, HR L10 against. Projection model targets 16.1 pts (4.4 pts below line; 60% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
@@ -12628,10 +12636,10 @@
         <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K76" t="n">
-        <v>1.82</v>
+        <v>1.385</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -12676,10 +12684,10 @@
         <v>1.3</v>
       </c>
       <c r="J77" t="n">
-        <v>1.885</v>
+        <v>2.75</v>
       </c>
       <c r="K77" t="n">
-        <v>1.847</v>
+        <v>1.417</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -12724,10 +12732,10 @@
         <v>0.2</v>
       </c>
       <c r="J78" t="n">
-        <v>1.935</v>
+        <v>2.75</v>
       </c>
       <c r="K78" t="n">
-        <v>1.8</v>
+        <v>1.417</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -12772,10 +12780,10 @@
         <v>0.2</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K79" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -12849,33 +12857,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.571</v>
+        <v>0.535</v>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>5.1</v>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="K81" t="n">
-        <v>1.417</v>
+        <v>1.345</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Wallace has a H2H avg of 5.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 5.0 pts is 5.4 below his season L30; His TS% shifts -11.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 7/10 signals agree (HR L30, HR L10, Trend, Defense among the strongest); Volume, Context dissent. Projection model targets 5.1 pts (2.4 pts below line; 57% blended confidence).</t>
+          <t>Wallace's L30 average of 10.4 pts is 3.9 above the 6.5 line, works against the UNDER. His H2H avg of 5.0 pts is 5.4 below his season L30; His TS% shifts -11.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 6/10 signals agree — HR L10, Trend, Defense support under; Volume, HR L30 against. Projection model targets 5.1 pts (1.4 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -12916,10 +12924,10 @@
         <v>2.2</v>
       </c>
       <c r="J82" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="K82" t="n">
-        <v>1.87</v>
+        <v>1.435</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -12964,10 +12972,10 @@
         <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>1.435</v>
+        <v>1.364</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -13045,29 +13053,29 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.522</v>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="K85" t="n">
-        <v>1.476</v>
+        <v>1.357</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Hart shows recent scoring up 4.4 pts vs L30 (L5 vs L30 trend). His H2H avg of 15.0 pts is 3.0 above his season L30; His TS% shifts -7.6% in this matchup. Opponent ranks as strong defense (#6) with slow pace (#28). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Defense dissent. Projection model targets 13.3 pts (1.8 pts above line; 56% blended confidence). Risk: high scoring volatility (σ=7.5) introduces outcome uncertainty.</t>
+          <t>Hart shows recent scoring up 4.4 pts vs L30 (L5 vs L30 trend). His H2H avg of 15.0 pts is 3.0 above his season L30; His TS% shifts -7.6% in this matchup. Opponent ranks as strong defense (#6) with slow pace (#28). 5/10 signals agree — Trend, Context, H2H support over; Volume, HR L30 against. Projection model targets 13.2 pts (0.7 pts above line; 52% blended confidence). Risk: high scoring volatility (σ=7.5) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -13108,10 +13116,10 @@
         <v>2.7</v>
       </c>
       <c r="J86" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K86" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -13156,10 +13164,10 @@
         <v>10.7</v>
       </c>
       <c r="J87" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K87" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -13252,10 +13260,10 @@
         <v>0.1</v>
       </c>
       <c r="J89" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K89" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -13300,10 +13308,10 @@
         <v>6</v>
       </c>
       <c r="J90" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="K90" t="n">
-        <v>1.417</v>
+        <v>1.408</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -13348,10 +13356,10 @@
         <v>2.4</v>
       </c>
       <c r="J91" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K91" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -13381,29 +13389,29 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.549</v>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Williams's L30 average of 17.7 pts vs line of 17.5, works against the UNDER. FG% trend +3.2% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#26). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.9 pts (2.6 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
+          <t>Williams's L30 average of 17.7 pts vs line of 16.5, works against the UNDER. FG% trend +3.2% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#26). Mixed signal picture: 3/10 agree. Agreeing: Defense, Pace, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.8 pts (1.7 pts below line; 54% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -13444,10 +13452,10 @@
         <v>5.2</v>
       </c>
       <c r="J93" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="K93" t="n">
-        <v>1.98</v>
+        <v>1.435</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -13458,7 +13466,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -13473,40 +13481,40 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>12.1</v>
+        <v>17.9</v>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="K94" t="n">
-        <v>1.787</v>
+        <v>1.345</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Green has a H2H avg of 12.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 12.0 pts is 3.6 above his season L30; His TS% shifts +14.6% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). 6/10 signals agree — Context, Defense, H2H support over; Volume, HR L30 against. Projection model targets 12.1 pts (3.6 pts above line; 60% blended confidence).</t>
+          <t>Podziemski shows recent scoring up 2.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.0% in this matchup. Opponent ranks as average defense (#11) with fast pace (#3). 5/10 signals agree — HR L30, Trend, Pace support over; Volume, HR L10 against. Projection model targets 17.9 pts (2.4 pts above line; 56% blended confidence). Risk: high scoring volatility (σ=7.4) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -13516,7 +13524,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13525,36 +13533,36 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.681</v>
+        <v>0.607</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>23.4</v>
+        <v>7</v>
       </c>
       <c r="I95" t="n">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K95" t="n">
-        <v>1.787</v>
+        <v>1.408</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Gordon has a H2H avg of 27.2 pts vs this opponent (+11.7 vs line) — supporting the OVER. His H2H avg of 27.2 pts is 11.7 above his season L30; His TS% shifts +20.5% in this matchup. Opponent ranks as average defense (#14) with above-average pace (#12). Mixed signal picture: 4/10 agree. Agreeing: HR L30, Context, H2H. Counter-signals: Volume, HR L10, Trend. Projection model targets 23.4 pts (7.9 pts above line; 68% blended confidence). Risk: high scoring volatility (σ=8.1) introduces outcome uncertainty.</t>
+          <t>Jr. has a H2H avg of 7.8 pts vs this opponent (-3.7 vs line) — supporting the UNDER. His H2H avg of 7.8 pts is 6.2 below his season L30; His TS% shifts -11.2% in this matchup. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 3/10 agree. Agreeing: H2H, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.0 pts (4.5 pts below line; 60% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -13573,36 +13581,36 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>17.9</v>
+        <v>13.6</v>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
-        <v>1.794</v>
+        <v>3.05</v>
       </c>
       <c r="K96" t="n">
-        <v>1.99</v>
+        <v>1.357</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Podziemski shows recent scoring up 2.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.0% in this matchup. Opponent ranks as average defense (#11) with fast pace (#3). 5/10 signals agree — HR L30, Trend, Pace support over; Volume, HR L10 against. Projection model targets 17.9 pts (2.4 pts above line; 56% blended confidence). Risk: high scoring volatility (σ=7.4) introduces outcome uncertainty.</t>
+          <t>Watson's L30 average of 18.2 pts is 5.7 above the 12.5 line, supports the OVER. His H2H avg of 7.2 pts is 11.0 below his season L30; His TS% shifts +8.0% in this matchup. Opponent ranks as below-average defense (#16) with above-average pace (#12). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 13.6 pts (1.1 pts above line; 54% blended confidence). Risk: L3 has dropped to 14.0 (4.2 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -13612,7 +13620,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13621,36 +13629,36 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.607</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>7</v>
+        <v>21.6</v>
       </c>
       <c r="I97" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
-        <v>1.806</v>
+        <v>3.05</v>
       </c>
       <c r="K97" t="n">
-        <v>1.98</v>
+        <v>1.357</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Jr. has a H2H avg of 7.8 pts vs this opponent (-3.7 vs line) — supporting the UNDER. His H2H avg of 7.8 pts is 6.2 below his season L30; His TS% shifts -11.2% in this matchup. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 3/10 agree. Agreeing: H2H, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.0 pts (4.5 pts below line; 60% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
+          <t>Porziņģis's L30 average of 17.4 pts vs line of 19.5, works against the OVER. Opponent ranks as below-average defense (#20) with fast pace (#3). Mixed signal picture: 2/10 agree. Agreeing: Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 21.6 pts (2.1 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=8.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -13660,7 +13668,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13669,36 +13677,36 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.54</v>
+        <v>0.516</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
-        <v>1.926</v>
+        <v>2.85</v>
       </c>
       <c r="K98" t="n">
-        <v>1.847</v>
+        <v>1.4</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Watson's L30 average of 18.2 pts is 5.7 above the 12.5 line, supports the OVER. His H2H avg of 7.2 pts is 11.0 below his season L30; His TS% shifts +8.0% in this matchup. Opponent ranks as below-average defense (#16) with above-average pace (#12). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 13.6 pts (1.1 pts above line; 54% blended confidence). Risk: L3 has dropped to 14.0 (4.2 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Santos has a H2H avg of 4.5 pts vs this opponent (-11.0 vs line) — supporting the UNDER. His H2H avg of 4.5 pts is 10.1 below his season L30; His TS% shifts +14.6% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 15.1 pts (0.4 pts below line; 51% blended confidence). Risk: L3 has surged to 24.7 after a 9-pt performance (10.1 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -13708,7 +13716,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13717,36 +13725,36 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.578</v>
+        <v>0.64</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J99" t="n">
-        <v>1.855</v>
+        <v>2.7</v>
       </c>
       <c r="K99" t="n">
-        <v>1.917</v>
+        <v>1.435</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Murray shows recent scoring up 6.7 pts vs L30 (L5 vs L30 trend). His H2H avg of 20.2 pts is 4.7 below his season L30. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 2/10 agree. Agreeing: H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 20.6 pts (2.9 pts below line; 57% blended confidence). Risk: L3 has surged to 35.0 after a 20-pt performance (10.1 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Melton shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). FG% trend -5.6% (L10 vs L30). Opponent ranks as average defense (#11) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 20.1 pts (5.6 pts above line; 64% blended confidence). Risk: high scoring volatility (σ=8.7) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -13756,7 +13764,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13765,36 +13773,36 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.544</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>27.9</v>
+        <v>9.6</v>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
-        <v>1.926</v>
+        <v>2.9</v>
       </c>
       <c r="K100" t="n">
-        <v>1.84</v>
+        <v>1.385</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Jokić has a H2H avg of 30.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His H2H avg of 30.6 pts is 3.6 above his season L30. Opponent ranks as below-average defense (#21) with above-average pace (#12). 7/10 signals agree (Volume, Context, Defense, H2H among the strongest); HR L30, HR L10 dissent. Projection model targets 27.9 pts (1.4 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=7.3) introduces outcome uncertainty.</t>
+          <t>Braun has a H2H avg of 12.6 pts vs this opponent (+2.1 vs line) — working against the UNDER. His TS% shifts -5.8% in this matchup; FG% trend +5.8% (L10 vs L30). Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 2/10 agree. Agreeing: Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.6 pts (0.9 pts below line; 55% blended confidence). Risk: 75% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -13809,40 +13817,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.55</v>
+        <v>0.602</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>21.6</v>
+        <v>12.1</v>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
-        <v>1.917</v>
+        <v>2.6</v>
       </c>
       <c r="K101" t="n">
-        <v>1.855</v>
+        <v>1.465</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Porziņģis's L30 average of 17.4 pts is 3.1 below the 20.5 line, works against the OVER. Opponent ranks as below-average defense (#20) with fast pace (#3). Mixed signal picture: 2/10 agree. Agreeing: Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 21.6 pts (1.1 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=8.1) introduces outcome uncertainty.</t>
+          <t>Green has a H2H avg of 12.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 12.0 pts is 3.6 above his season L30; His TS% shifts +14.6% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). 6/10 signals agree — Context, Defense, H2H support over; Volume, HR L30 against. Projection model targets 12.1 pts (3.6 pts above line; 60% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -13857,40 +13865,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.592</v>
+        <v>0.681</v>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>13.8</v>
+        <v>23.4</v>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="J102" t="n">
-        <v>1.826</v>
+        <v>2.7</v>
       </c>
       <c r="K102" t="n">
-        <v>1.943</v>
+        <v>1.435</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>II shows recent scoring up 4.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +14.0% in this matchup; FG% trend +15.7% (L10 vs L30). Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — HR L30, HR L10, Trend support over; Volume, Context against. Projection model targets 13.8 pts (2.3 pts above line; 59% blended confidence).</t>
+          <t>Gordon has a H2H avg of 27.2 pts vs this opponent (+11.7 vs line) — supporting the OVER. His H2H avg of 27.2 pts is 11.7 above his season L30; His TS% shifts +20.5% in this matchup. Opponent ranks as average defense (#14) with above-average pace (#12). Mixed signal picture: 4/10 agree. Agreeing: HR L30, Context, H2H. Counter-signals: Volume, HR L10, Trend. Projection model targets 23.4 pts (7.9 pts above line; 68% blended confidence). Risk: high scoring volatility (σ=8.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -13909,36 +13917,36 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.516</v>
+        <v>0.578</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>15.1</v>
+        <v>20.6</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J103" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K103" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Santos has a H2H avg of 4.5 pts vs this opponent (-11.0 vs line) — supporting the UNDER. His H2H avg of 4.5 pts is 10.1 below his season L30; His TS% shifts +14.6% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 15.1 pts (0.4 pts below line; 51% blended confidence). Risk: L3 has surged to 24.7 after a 9-pt performance (10.1 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Murray shows recent scoring up 6.7 pts vs L30 (L5 vs L30 trend). His H2H avg of 20.2 pts is 4.7 below his season L30. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 2/10 agree. Agreeing: H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 20.6 pts (2.9 pts below line; 57% blended confidence). Risk: L3 has surged to 35.0 after a 20-pt performance (10.1 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -13957,36 +13965,36 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.64</v>
+        <v>0.544</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>20.1</v>
+        <v>27.9</v>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
-        <v>1.847</v>
+        <v>3.15</v>
       </c>
       <c r="K104" t="n">
-        <v>1.926</v>
+        <v>1.333</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Melton shows recent scoring down 4.5 pts vs L30 (L5 vs L30 trend). FG% trend -5.6% (L10 vs L30). Opponent ranks as average defense (#11) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 20.1 pts (5.6 pts above line; 64% blended confidence). Risk: high scoring volatility (σ=8.7) introduces outcome uncertainty.</t>
+          <t>Jokić has a H2H avg of 30.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His H2H avg of 30.6 pts is 3.6 above his season L30. Opponent ranks as below-average defense (#21) with above-average pace (#12). 7/10 signals agree (Volume, Context, Defense, H2H among the strongest); HR L30, HR L10 dissent. Projection model targets 27.9 pts (1.4 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=7.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -13996,38 +14004,38 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>9.6</v>
+        <v>13.8</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
-        <v>1.909</v>
+        <v>2.8</v>
       </c>
       <c r="K105" t="n">
-        <v>1.862</v>
+        <v>1.408</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Braun has a H2H avg of 12.6 pts vs this opponent (+2.1 vs line) — working against the UNDER. His TS% shifts -5.8% in this matchup; FG% trend +5.8% (L10 vs L30). Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 2/10 agree. Agreeing: Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.6 pts (0.9 pts below line; 55% blended confidence). Risk: 75% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>II shows recent scoring up 4.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +14.0% in this matchup; FG% trend +15.7% (L10 vs L30). Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — HR L30, HR L10, Trend support over; Volume, Context against. Projection model targets 13.8 pts (2.3 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14142,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="4">
@@ -14190,11 +14198,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="7">
@@ -14234,7 +14242,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="9">
@@ -14254,7 +14262,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="10">
@@ -14330,17 +14338,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14354,13 +14362,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -14374,13 +14382,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14474,7 +14482,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -14494,7 +14502,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22">
@@ -14520,7 +14528,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -14534,33 +14542,33 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOS @ CHA</t>
+          <t>MIA @ IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -14574,13 +14582,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -14594,13 +14602,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -14610,17 +14618,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -14630,11 +14638,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="29">
@@ -14734,7 +14742,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="34">
@@ -14770,17 +14778,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14794,7 +14802,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -14854,7 +14862,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="40">
@@ -15034,7 +15042,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="49">
@@ -15134,7 +15142,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="54">
@@ -15174,7 +15182,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="56">
@@ -15200,7 +15208,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -15214,13 +15222,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15240,7 +15248,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15254,13 +15262,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sidy Cissoko</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15274,13 +15282,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15294,13 +15302,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15314,13 +15322,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15334,13 +15342,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15354,13 +15362,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Sidy Cissoko</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -15374,13 +15382,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -15394,7 +15402,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="67">
@@ -15434,7 +15442,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="69">
@@ -15574,7 +15582,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="76">
@@ -15694,7 +15702,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="82">
@@ -15774,7 +15782,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="86">
@@ -15914,7 +15922,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="93">
@@ -15940,7 +15948,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15954,13 +15962,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -15970,17 +15978,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15994,13 +16002,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -16010,17 +16018,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -16030,17 +16038,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -16050,17 +16058,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>23.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -16070,17 +16078,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>26.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -16094,13 +16102,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>20.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gary Payton II</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -16114,13 +16122,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -16134,13 +16142,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -16154,13 +16162,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>14.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Gary Payton II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -16170,11 +16178,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-03-29.xlsx
+++ b/daily/2026-03-29.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -629,7 +643,6 @@
       <c r="V2" t="n">
         <v>27</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>-24.6</v>
       </c>
@@ -1035,7 +1048,6 @@
       <c r="V7" t="n">
         <v>13</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>11.8</v>
       </c>
@@ -1113,7 +1125,6 @@
       <c r="V8" t="n">
         <v>13</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>2</v>
       </c>
@@ -1191,7 +1202,6 @@
       <c r="V9" t="n">
         <v>13</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>48.6</v>
       </c>
@@ -1925,7 +1935,6 @@
       <c r="V18" t="n">
         <v>4</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>-2.8</v>
       </c>
@@ -2648,7 +2657,7 @@
         <v>-3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>-0.3</v>
@@ -2987,7 +2996,6 @@
       <c r="V31" t="n">
         <v>24</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>-3.6</v>
       </c>
@@ -3311,7 +3319,6 @@
       <c r="V35" t="n">
         <v>24</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>0.4</v>
       </c>
@@ -3372,7 +3379,7 @@
         <v>45</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>-4.1</v>
@@ -3635,7 +3642,6 @@
       <c r="V39" t="n">
         <v>30</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>17</v>
       </c>
@@ -3778,7 +3784,7 @@
         <v>50</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>-0.5</v>
@@ -3795,7 +3801,6 @@
       <c r="V41" t="n">
         <v>15</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>20.1</v>
       </c>
@@ -3873,7 +3878,6 @@
       <c r="V42" t="n">
         <v>15</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>-11.1</v>
       </c>
@@ -3951,7 +3955,6 @@
       <c r="V43" t="n">
         <v>15</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>15.9</v>
       </c>
@@ -4029,7 +4032,6 @@
       <c r="V44" t="n">
         <v>30</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>13.1</v>
       </c>
@@ -4107,7 +4109,6 @@
       <c r="V45" t="n">
         <v>30</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>4.6</v>
       </c>
@@ -4185,7 +4186,6 @@
       <c r="V46" t="n">
         <v>25</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-14.3</v>
       </c>
@@ -4509,7 +4509,6 @@
       <c r="V50" t="n">
         <v>25</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>-9</v>
       </c>
@@ -5079,7 +5078,6 @@
       <c r="V57" t="n">
         <v>19</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>21</v>
       </c>
@@ -5239,7 +5237,6 @@
       <c r="V59" t="n">
         <v>11</v>
       </c>
-      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>6.1</v>
       </c>
@@ -5317,7 +5314,6 @@
       <c r="V60" t="n">
         <v>19</v>
       </c>
-      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>-5</v>
       </c>
@@ -5395,7 +5391,6 @@
       <c r="V61" t="n">
         <v>11</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>-4</v>
       </c>
@@ -5473,7 +5468,6 @@
       <c r="V62" t="n">
         <v>19</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
         <v>45.8</v>
       </c>
@@ -5551,7 +5545,6 @@
       <c r="V63" t="n">
         <v>11</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
         <v>0</v>
       </c>
@@ -5711,7 +5704,6 @@
       <c r="V65" t="n">
         <v>11</v>
       </c>
-      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>-46.2</v>
       </c>
@@ -7101,7 +7093,6 @@
       <c r="V82" t="n">
         <v>26</v>
       </c>
-      <c r="W82" t="inlineStr"/>
       <c r="X82" t="n">
         <v>26.8</v>
       </c>
@@ -7425,7 +7416,6 @@
       <c r="V86" t="n">
         <v>26</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-1.2</v>
       </c>
@@ -7503,7 +7493,6 @@
       <c r="V87" t="n">
         <v>26</v>
       </c>
-      <c r="W87" t="inlineStr"/>
       <c r="X87" t="n">
         <v>11.7</v>
       </c>
@@ -7581,7 +7570,6 @@
       <c r="V88" t="n">
         <v>28</v>
       </c>
-      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>0</v>
       </c>
@@ -7905,7 +7893,6 @@
       <c r="V92" t="n">
         <v>26</v>
       </c>
-      <c r="W92" t="inlineStr"/>
       <c r="X92" t="n">
         <v>-4.1</v>
       </c>
@@ -8311,7 +8298,6 @@
       <c r="V97" t="n">
         <v>3</v>
       </c>
-      <c r="W97" t="inlineStr"/>
       <c r="X97" t="n">
         <v>8.4</v>
       </c>
@@ -8471,7 +8457,6 @@
       <c r="V99" t="n">
         <v>3</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>1.2</v>
       </c>
@@ -14124,25 +14109,63 @@
       <c r="D2" t="n">
         <v>19.5</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>13.5</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 13.5 line, -6.5). Projection model called 7.1 pts — actual 7 was 0.1 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -14164,125 +14187,293 @@
       <c r="D4" t="n">
         <v>10.5</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 19.5 line, -4.5). Projection model targeted 20.8 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: H2H, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (20 pts vs 27.5 line, -7.5). Projection model (28.4 pts) and actual (20) both missed the mark. Key signals that disagreed: Trend, H2H. Counter-signals that proved correct: Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (10 pts vs 5.5 line, +4.5). Projection model targeted 4.2 pts (correct direction) but actual was 10. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (22 pts vs 10.5 line, +11.5). Overperformed by 11.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 10.5 line, -2.5). Projection model targeted 14.1 pts (correct direction) but actual was 8. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 9.5 line, +3.5). Projection model targeted 6.0 pts (correct direction) but actual was 13. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -14304,65 +14495,155 @@
       <c r="D11" t="n">
         <v>11.5</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (28 pts vs 17.5 line, +10.5). Overperformed by 10.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Kel'el Ware</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 9.5 line, -4.5).</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 9.5 line, +2.5). Projection model targeted 4.3 pts (correct direction) but actual was 12. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -14384,165 +14665,385 @@
       <c r="D15" t="n">
         <v>13.5</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 12.5 line, +2.5). Projection model targeted 10.9 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L10, Defense.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (15 pts vs 12.5 line, +2.5). Projection model called 15.3 pts — actual 15 was 0.3 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 9.5 line, -3.5). Projection model (10.3 pts) and actual (6) both missed the mark. Key signals that disagreed: HR L10, Trend, Defense. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Andrew Nembhard</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 15.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 22.5 line, -7.5). Projection model targeted 25.6 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (31 pts vs 22.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (30 pts vs 22.5 line, +7.5).</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>14.5</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 14.5 line, +2.5). Projection model targeted 11.3 pts (correct direction) but actual was 17. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -14564,45 +15065,109 @@
       <c r="D24" t="n">
         <v>11.5</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (19 pts vs 19.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>18.5</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (28 pts vs 18.5 line, +9.5).</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -14624,205 +15189,477 @@
       <c r="D27" t="n">
         <v>17.5</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (32 pts vs 23.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, H2H.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 13.5 line, -2.5). Projection model called 11.0 pts — actual 11 was 0.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 7.5 line, -3.5). Projection model called 6.5 pts — actual 4 was 2.5 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 19.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Baylor Scheierman</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (14 pts vs 6.5 line, +7.5).</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 9.5 line, +7.5). Projection model targeted 6.2 pts (correct direction) but actual was 17. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Min Trend.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 14.5 line, -0.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (13 pts vs 17.5 line, -4.5). Projection model (18.1 pts) and actual (13) both missed the mark. Key signals that disagreed: HR L10, Trend, Defense. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 9.5 line, -2.5). Projection model called 9.1 pts — actual 7 was 2.1 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>13.5</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 13.5 line, +2.5). Projection model called 17.7 pts — actual 16 was 1.7 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -14844,25 +15681,63 @@
       <c r="D38" t="n">
         <v>18.5</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>16.5</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (13 pts vs 16.5 line, -3.5). Projection model targeted 22.4 pts (correct direction) but actual was 13. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -14884,65 +15759,155 @@
       <c r="D40" t="n">
         <v>11.5</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 10.5 line, +6.5). Projection model called 17.3 pts — actual 17 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 8.5 line, +7.5). Projection model targeted 6.9 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 9.5 line, +5.5). Projection model (9.5 pts) and actual (15) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -14964,85 +15929,201 @@
       <c r="D44" t="n">
         <v>14.5</v>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 12.5 line, +7.5). Projection model (12.1 pts) and actual (20) both missed the mark. Key signals that disagreed: HR L10, Trend, Defense. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Jamal Cain</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (0 pts vs 8.5 line, -8.5). Projection model called 2.5 pts — actual 0 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (17 pts vs 21.5 line, -4.5). Projection model targeted 25.1 pts (correct direction) but actual was 17. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>11.5</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 11.5 line, +0.5). Projection model called 13.6 pts — actual 12 was 1.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -15064,545 +16145,1259 @@
       <c r="D49" t="n">
         <v>22.5</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 13.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (24 pts vs 20.5 line, +3.5). Projection model targeted 16.9 pts (correct direction) but actual was 24. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, FG Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 18.5 line, +4.5). Projection model targeted 14.2 pts (correct direction) but actual was 23. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: FG Trend.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (11 pts vs 10.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (9 pts vs 24.5 line, -15.5). Underperformed by 15.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Defense, Pace, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 11.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 11.5 line, -7.5).</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 12.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 16.5 line, -10.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 14.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Tristan Vukcevic</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 12.5 line, -2.5). Projection model called 11.4 pts — actual 10 was 1.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 16.5 line, +4.5). Projection model targeted 15.1 pts (correct direction) but actual was 21. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 16.5 line, -2.5).</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 8.5 line, -4.5). Projection model called 5.7 pts — actual 4 was 1.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 17.5 line, -6.5). Projection model called 10.6 pts — actual 11 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Sidy Cissoko</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (1 pts vs 7.5 line, -6.5). Projection model called -0.1 pts — actual 1 was 1.1 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (20 pts vs 26.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (36 pts vs 20.5 line, +15.5). Overperformed by 15.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 15.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E69" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (20 pts vs 24.5 line, -4.5). Projection model (24.3 pts) and actual (20) both missed the mark. Key signals that disagreed: Min Trend. Counter-signals that proved correct: Min Trend.</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 7.5 line, +5.5).</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Dejounte Murray</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (19 pts vs 15.5 line, +3.5). Projection model called 19.8 pts — actual 19 was 0.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (10 pts vs 9.5 line, +0.5). Projection model called 12.4 pts — actual 10 was 2.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (14 pts vs 18.5 line, -4.5). Projection model (18.6 pts) and actual (14) both missed the mark. Key signals that disagreed: Volume, Context, H2H. Counter-signals that proved correct: Volume, Context, H2H.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 8.5 line, +6.5). Projection model (8.4 pts) and actual (15) both missed the mark. Key signals that disagreed: Volume, Defense, H2H. Counter-signals that proved correct: Volume, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 20.5 line, -2.5). Projection model called 16.1 pts — actual 18 was 1.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>15.5</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (20 pts vs 15.5 line, +4.5). Projection model called 17.5 pts — actual 20 was 2.5 off. Model accuracy strong on this play. Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -15624,485 +17419,1121 @@
       <c r="D77" t="n">
         <v>20.5</v>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 17.5 line, +0.5). Projection model called 17.7 pts — actual 18 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 17.5 line, -2.5). Projection model (17.3 pts) and actual (15) both missed the mark. Key signals that disagreed: Defense, Pace. Counter-signals that proved correct: Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (32 pts vs 24.5 line, +7.5). Projection model targeted 18.1 pts (correct direction) but actual was 32. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 6.5 line, -1.5). Projection model called 5.1 pts — actual 5 was 0.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Alex Caruso</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (6 pts vs 5.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E83" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 12.5 line, +2.5). Projection model targeted 9.5 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, H2H.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 6.5 line, +5.5). Projection model (6.4 pts) and actual (12) both missed the mark. Key signals that disagreed: Volume, HR L30, Context. Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E85" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (15 pts vs 12.5 line, +2.5). Projection model called 13.2 pts — actual 15 was 1.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 11.5 line, -3.5). Projection model called 8.8 pts — actual 8 was 0.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E87" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 15.5 line, +0.5).</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>4.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 4.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>30.5</v>
       </c>
+      <c r="E89" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (30 pts vs 30.5 line, -0.5). Projection model called 30.4 pts — actual 30 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 7.5 line, -1.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 15.5 line, -5.5).</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (22 pts vs 16.5 line, +5.5). Projection model targeted 14.8 pts (correct direction) but actual was 22. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 11.5 line, -5.5). Projection model called 6.3 pts — actual 6 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (23 pts vs 15.5 line, +7.5).</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 11.5 line, +4.5). Projection model targeted 7.0 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Peyton Watson</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (10 pts vs 12.5 line, -2.5). Projection model targeted 13.6 pts (correct direction) but actual was 10. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, H2H, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (23 pts vs 19.5 line, +3.5). Projection model called 21.6 pts — actual 23 was 1.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E98" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 15.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (0 pts vs 14.5 line, -14.5). Underperformed by 14.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 10.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="3" t="n">
         <v>8.5</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 8.5 line, +4.5). Projection model called 12.1 pts — actual 13 was 0.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -16124,65 +18555,155 @@
       <c r="D102" t="n">
         <v>15.5</v>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E103" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (20 pts vs 23.5 line, -3.5). Projection model called 20.6 pts — actual 20 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (25 pts vs 26.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="3" t="n">
         <v>11.5</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 11.5 line, +4.5). Projection model called 13.8 pts — actual 16 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
